--- a/Inputs_EmpresaX.xlsx
+++ b/Inputs_EmpresaX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kaizen\Documents\tese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358D41FB-D1BC-42A1-91AE-CA373AD38640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C72EABB-EEF4-4113-AF00-641176C2A83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -757,8 +757,26 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={C7364A66-A497-423F-B38F-AF51BEC19DB7}</author>
+  </authors>
+  <commentList>
+    <comment ref="J78" authorId="0" shapeId="0" xr:uid="{C7364A66-A497-423F-B38F-AF51BEC19DB7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    900</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="533">
   <si>
     <t>ESTRUTURA FÍSICA DO SISTEMA PRODUTIVO</t>
   </si>
@@ -2342,17 +2360,33 @@
   </si>
   <si>
     <t>DC102600</t>
+  </si>
+  <si>
+    <t>Line</t>
+  </si>
+  <si>
+    <t>Total Occupied Hours</t>
+  </si>
+  <si>
+    <t>Total Available Hours</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>L2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General\ &quot;min&quot;"/>
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2488,8 +2522,28 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2539,8 +2593,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -2654,11 +2714,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2825,16 +2900,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2852,11 +2927,33 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3588,27 +3685,33 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Raquel Duque" id="{DAA1B03B-E46D-4B86-913A-0A7B4214C9B3}" userId="S::rduque@kaizen.com::276b5b66-a20e-4e3a-b701-a469ee4d4468" providerId="AD"/>
+</personList>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A2E0425D-8D3D-4317-A507-ADC777C31517}" name="Table4" displayName="Table4" ref="A4:Q192" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18" tableBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A2E0425D-8D3D-4317-A507-ADC777C31517}" name="Table4" displayName="Table4" ref="A4:Q192" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
   <autoFilter ref="A4:Q192" xr:uid="{A2E0425D-8D3D-4317-A507-ADC777C31517}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{26D481BD-1A66-4F75-A5DB-835BDEAD35EC}" name="ref_id" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{AF3D888D-29CC-4818-9F37-35E1C095FEBC}" name="nome" dataDxfId="15"/>
-    <tableColumn id="21" xr3:uid="{A36D18E5-0E2F-48D2-A9EA-1667409CF7FA}" name="Unid_caixa" dataDxfId="14"/>
-    <tableColumn id="19" xr3:uid="{901BF69A-B9CB-436F-8A73-E52E627A4C44}" name="nao_produzir_segunda" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{73E06642-D2DC-4B3F-B7AE-6A99CF0B73CD}" name="família" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{47F7E5B0-45A6-4E01-8304-DD4D19A9E24E}" name="ativa" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{E576D14B-BDA0-4CA6-B2F4-097D5C1CE99B}" name="pode_L1" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{B29DBEC4-DD50-4914-98AC-30F025559FDC}" name="tempo_L1_prod_min (cadência de L1)" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{14DD02B2-C00E-494B-A8F3-3FFAE31BC4FB}" name="operadores_nec_L1_acab" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{89492EE9-DE84-43EE-B12E-2605FE3EAD79}" name="operadores_nec_L1_prod" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{780BF028-7B4E-42E1-B807-EDB2FB22CEE7}" name="pode_L2" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{FD12F15B-F3BE-48A4-B186-794E71F468D8}" name="tempo_L2_prod_min (cadência de L2)" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{2B695F9C-3774-41DD-8FE4-AF094E98B022}" name="tempo_L2_acab_min (cadência de L2)" dataDxfId="4"/>
-    <tableColumn id="20" xr3:uid="{46C45284-5F2B-442A-A3EB-D66468126784}" name="operadores_nec_L2_acab" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{1453032D-3307-46D2-BB7E-3D55B4D2E43D}" name="operadores_nec_L2_prod" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{5009F860-773A-42AE-9780-72CCCE321658}" name="kg" dataDxfId="1"/>
-    <tableColumn id="18" xr3:uid="{3939DDEA-30DE-43D1-B600-33ECEC5CD680}" name="euros" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{26D481BD-1A66-4F75-A5DB-835BDEAD35EC}" name="ref_id" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{AF3D888D-29CC-4818-9F37-35E1C095FEBC}" name="nome" dataDxfId="16"/>
+    <tableColumn id="21" xr3:uid="{A36D18E5-0E2F-48D2-A9EA-1667409CF7FA}" name="Unid_caixa" dataDxfId="15"/>
+    <tableColumn id="19" xr3:uid="{901BF69A-B9CB-436F-8A73-E52E627A4C44}" name="nao_produzir_segunda" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{73E06642-D2DC-4B3F-B7AE-6A99CF0B73CD}" name="família" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{47F7E5B0-45A6-4E01-8304-DD4D19A9E24E}" name="ativa" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{E576D14B-BDA0-4CA6-B2F4-097D5C1CE99B}" name="pode_L1" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{B29DBEC4-DD50-4914-98AC-30F025559FDC}" name="tempo_L1_prod_min (cadência de L1)" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{14DD02B2-C00E-494B-A8F3-3FFAE31BC4FB}" name="operadores_nec_L1_acab" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{89492EE9-DE84-43EE-B12E-2605FE3EAD79}" name="operadores_nec_L1_prod" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{780BF028-7B4E-42E1-B807-EDB2FB22CEE7}" name="pode_L2" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{FD12F15B-F3BE-48A4-B186-794E71F468D8}" name="tempo_L2_prod_min (cadência de L2)" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{2B695F9C-3774-41DD-8FE4-AF094E98B022}" name="tempo_L2_acab_min (cadência de L2)" dataDxfId="5"/>
+    <tableColumn id="20" xr3:uid="{46C45284-5F2B-442A-A3EB-D66468126784}" name="operadores_nec_L2_acab" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{1453032D-3307-46D2-BB7E-3D55B4D2E43D}" name="operadores_nec_L2_prod" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{5009F860-773A-42AE-9780-72CCCE321658}" name="kg" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{3939DDEA-30DE-43D1-B600-33ECEC5CD680}" name="euros" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3897,6 +4000,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="J78" dT="2026-05-21T13:53:57.62" personId="{DAA1B03B-E46D-4B86-913A-0A7B4214C9B3}" id="{C7364A66-A497-423F-B38F-AF51BEC19DB7}">
+    <text>900</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
   <wetp:taskpane dockstate="right" visibility="0" width="525" row="9">
@@ -3983,7 +4094,7 @@
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="58" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="59"/>
@@ -4020,7 +4131,7 @@
       <c r="C9" s="3"/>
     </row>
     <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="62" t="s">
+      <c r="A11" s="58" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="59"/>
@@ -4048,7 +4159,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="62" t="s">
+      <c r="A15" s="58" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="59"/>
@@ -4134,7 +4245,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="62" t="s">
+      <c r="A24" s="58" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="59"/>
@@ -4218,7 +4329,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="62" t="s">
+      <c r="A33" s="58" t="s">
         <v>21</v>
       </c>
       <c r="B33" s="59"/>
@@ -4247,64 +4358,59 @@
       <c r="A39" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="61"/>
-      <c r="C39" s="61"/>
+      <c r="B39" s="62"/>
+      <c r="C39" s="62"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="61"/>
-      <c r="C40" s="61"/>
+      <c r="B40" s="62"/>
+      <c r="C40" s="62"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="64"/>
-      <c r="B41" s="61"/>
-      <c r="C41" s="61"/>
+      <c r="B41" s="62"/>
+      <c r="C41" s="62"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="61"/>
-      <c r="C42" s="61"/>
+      <c r="B42" s="62"/>
+      <c r="C42" s="62"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="60" t="s">
+      <c r="A43" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="61"/>
-      <c r="C43" s="61"/>
+      <c r="B43" s="62"/>
+      <c r="C43" s="62"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="61"/>
-      <c r="C44" s="61"/>
+      <c r="B44" s="62"/>
+      <c r="C44" s="62"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="58"/>
+      <c r="A45" s="60"/>
       <c r="B45" s="59"/>
       <c r="C45" s="59"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="58"/>
+      <c r="A46" s="60"/>
       <c r="B46" s="59"/>
       <c r="C46" s="59"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="58"/>
+      <c r="A47" s="60"/>
       <c r="B47" s="59"/>
       <c r="C47" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A46:C46"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A43:C43"/>
@@ -4316,6 +4422,11 @@
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A46:C46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14520,7 +14631,7 @@
         <v>22</v>
       </c>
       <c r="G191" s="45" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H191" s="43" t="s">
         <v>35</v>
@@ -18739,30 +18850,34 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="B1:F86"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="B1:J85"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14" style="6" customWidth="1"/>
     <col min="3" max="3" width="18" style="14" customWidth="1"/>
     <col min="4" max="4" width="24.26953125" style="38" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" customWidth="1"/>
+    <col min="7" max="7" width="25.08984375" customWidth="1"/>
+    <col min="8" max="8" width="29.90625" customWidth="1"/>
+    <col min="11" max="11" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B1" s="57" t="s">
         <v>36</v>
       </c>
       <c r="C1" s="56"/>
       <c r="D1" s="56"/>
     </row>
-    <row r="2" spans="2:6" ht="35" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="55" t="s">
         <v>404</v>
       </c>
       <c r="C2" s="56"/>
       <c r="D2" s="56"/>
     </row>
-    <row r="4" spans="2:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" ht="45" x14ac:dyDescent="0.35">
       <c r="B4" s="35" t="s">
         <v>28</v>
       </c>
@@ -18772,8 +18887,17 @@
       <c r="D4" s="36" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="F4" s="69" t="s">
+        <v>528</v>
+      </c>
+      <c r="G4" s="69" t="s">
+        <v>529</v>
+      </c>
+      <c r="H4" s="69" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B5" s="34" t="s">
         <v>224</v>
       </c>
@@ -18783,16 +18907,17 @@
       <c r="D5" s="37">
         <v>46203</v>
       </c>
-      <c r="E5">
-        <f>_xlfn.XLOOKUP(B5,Table4[ref_id],Table4[euros])</f>
-        <v>20.22</v>
-      </c>
-      <c r="F5">
-        <f>E5*C5</f>
-        <v>3396.96</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="F5" s="70" t="s">
+        <v>531</v>
+      </c>
+      <c r="G5" s="71">
+        <v>165.92526540126542</v>
+      </c>
+      <c r="H5" s="72">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B6" s="34" t="s">
         <v>229</v>
       </c>
@@ -18802,16 +18927,17 @@
       <c r="D6" s="37">
         <v>46203</v>
       </c>
-      <c r="E6">
-        <f>_xlfn.XLOOKUP(B6,Table4[ref_id],Table4[euros])</f>
-        <v>25.88</v>
-      </c>
-      <c r="F6">
-        <f t="shared" ref="F6:F52" si="0">E6*C6</f>
-        <v>4347.84</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="F6" s="70" t="s">
+        <v>532</v>
+      </c>
+      <c r="G6" s="71">
+        <v>241.03174325966435</v>
+      </c>
+      <c r="H6" s="72">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="34" t="s">
         <v>372</v>
       </c>
@@ -18821,18 +18947,10 @@
       <c r="D7" s="37">
         <v>46177</v>
       </c>
-      <c r="E7">
-        <f>_xlfn.XLOOKUP(B7,Table4[ref_id],Table4[euros])</f>
-        <v>16.989999999999998</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="0"/>
-        <v>9786.24</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="34" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C8" s="34">
         <v>140</v>
@@ -18840,16 +18958,8 @@
       <c r="D8" s="37">
         <v>46203</v>
       </c>
-      <c r="E8">
-        <f>_xlfn.XLOOKUP(B8,Table4[ref_id],Table4[euros])</f>
-        <v>19.87</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="0"/>
-        <v>2781.8</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="34" t="s">
         <v>234</v>
       </c>
@@ -18859,16 +18969,8 @@
       <c r="D9" s="37">
         <v>46203</v>
       </c>
-      <c r="E9">
-        <f>_xlfn.XLOOKUP(B9,Table4[ref_id],Table4[euros])</f>
-        <v>17.11</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="0"/>
-        <v>2395.4</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B10" s="34" t="s">
         <v>259</v>
       </c>
@@ -18878,16 +18980,8 @@
       <c r="D10" s="37">
         <v>46203</v>
       </c>
-      <c r="E10">
-        <f>_xlfn.XLOOKUP(B10,Table4[ref_id],Table4[euros])</f>
-        <v>21</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="0"/>
-        <v>6300</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B11" s="34" t="s">
         <v>374</v>
       </c>
@@ -18897,16 +18991,8 @@
       <c r="D11" s="37">
         <v>46203</v>
       </c>
-      <c r="E11">
-        <f>_xlfn.XLOOKUP(B11,Table4[ref_id],Table4[euros])</f>
-        <v>9.85</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
-        <v>2521.6</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B12" s="34" t="s">
         <v>269</v>
       </c>
@@ -18916,16 +19002,8 @@
       <c r="D12" s="37">
         <v>46203</v>
       </c>
-      <c r="E12">
-        <f>_xlfn.XLOOKUP(B12,Table4[ref_id],Table4[euros])</f>
-        <v>17.260000000000002</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
-        <v>4142.4000000000005</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B13" s="34" t="s">
         <v>306</v>
       </c>
@@ -18935,16 +19013,8 @@
       <c r="D13" s="37">
         <v>46203</v>
       </c>
-      <c r="E13">
-        <f>_xlfn.XLOOKUP(B13,Table4[ref_id],Table4[euros])</f>
-        <v>28.47</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="0"/>
-        <v>5466.24</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B14" s="34" t="s">
         <v>318</v>
       </c>
@@ -18954,16 +19024,8 @@
       <c r="D14" s="37">
         <v>46203</v>
       </c>
-      <c r="E14">
-        <f>_xlfn.XLOOKUP(B14,Table4[ref_id],Table4[euros])</f>
-        <v>18.72</v>
-      </c>
-      <c r="F14">
-        <f t="shared" si="0"/>
-        <v>4492.7999999999993</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B15" s="34" t="s">
         <v>322</v>
       </c>
@@ -18973,16 +19035,8 @@
       <c r="D15" s="37">
         <v>46203</v>
       </c>
-      <c r="E15">
-        <f>_xlfn.XLOOKUP(B15,Table4[ref_id],Table4[euros])</f>
-        <v>28.81</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="0"/>
-        <v>4148.6399999999994</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B16" s="34" t="s">
         <v>337</v>
       </c>
@@ -18992,16 +19046,8 @@
       <c r="D16" s="37">
         <v>46177</v>
       </c>
-      <c r="E16">
-        <f>_xlfn.XLOOKUP(B16,Table4[ref_id],Table4[euros])</f>
-        <v>16.559999999999999</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="0"/>
-        <v>1788.4799999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="34" t="s">
         <v>378</v>
       </c>
@@ -19011,16 +19057,8 @@
       <c r="D17" s="37">
         <v>46203</v>
       </c>
-      <c r="E17">
-        <f>_xlfn.XLOOKUP(B17,Table4[ref_id],Table4[euros])</f>
-        <v>15.67</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="0"/>
-        <v>6769.44</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="34" t="s">
         <v>512</v>
       </c>
@@ -19030,16 +19068,8 @@
       <c r="D18" s="37">
         <v>46203</v>
       </c>
-      <c r="E18">
-        <f>_xlfn.XLOOKUP(B18,Table4[ref_id],Table4[euros])</f>
-        <v>39.58</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="0"/>
-        <v>3324.72</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="34" t="s">
         <v>239</v>
       </c>
@@ -19049,16 +19079,8 @@
       <c r="D19" s="37">
         <v>46203</v>
       </c>
-      <c r="E19">
-        <f>_xlfn.XLOOKUP(B19,Table4[ref_id],Table4[euros])</f>
-        <v>25.4</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="0"/>
-        <v>2235.1999999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="34" t="s">
         <v>242</v>
       </c>
@@ -19068,16 +19090,8 @@
       <c r="D20" s="37">
         <v>46203</v>
       </c>
-      <c r="E20">
-        <f>_xlfn.XLOOKUP(B20,Table4[ref_id],Table4[euros])</f>
-        <v>18.73</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="0"/>
-        <v>14047.5</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="34" t="s">
         <v>243</v>
       </c>
@@ -19087,16 +19101,8 @@
       <c r="D21" s="37">
         <v>46203</v>
       </c>
-      <c r="E21">
-        <f>_xlfn.XLOOKUP(B21,Table4[ref_id],Table4[euros])</f>
-        <v>18.46</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="0"/>
-        <v>3692</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="34" t="s">
         <v>244</v>
       </c>
@@ -19106,16 +19112,8 @@
       <c r="D22" s="37">
         <v>46203</v>
       </c>
-      <c r="E22">
-        <f>_xlfn.XLOOKUP(B22,Table4[ref_id],Table4[euros])</f>
-        <v>19.350000000000001</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="0"/>
-        <v>1935.0000000000002</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="34" t="s">
         <v>245</v>
       </c>
@@ -19125,16 +19123,8 @@
       <c r="D23" s="37">
         <v>46203</v>
       </c>
-      <c r="E23">
-        <f>_xlfn.XLOOKUP(B23,Table4[ref_id],Table4[euros])</f>
-        <v>20.69</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="0"/>
-        <v>5462.1600000000008</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="34" t="s">
         <v>246</v>
       </c>
@@ -19144,16 +19134,8 @@
       <c r="D24" s="37">
         <v>46203</v>
       </c>
-      <c r="E24">
-        <f>_xlfn.XLOOKUP(B24,Table4[ref_id],Table4[euros])</f>
-        <v>19.829999999999998</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="0"/>
-        <v>951.83999999999992</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="34" t="s">
         <v>252</v>
       </c>
@@ -19163,16 +19145,8 @@
       <c r="D25" s="37">
         <v>46203</v>
       </c>
-      <c r="E25">
-        <f>_xlfn.XLOOKUP(B25,Table4[ref_id],Table4[euros])</f>
-        <v>21.47</v>
-      </c>
-      <c r="F25">
-        <f t="shared" si="0"/>
-        <v>1030.56</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="34" t="s">
         <v>249</v>
       </c>
@@ -19182,16 +19156,8 @@
       <c r="D26" s="37">
         <v>46203</v>
       </c>
-      <c r="E26">
-        <f>_xlfn.XLOOKUP(B26,Table4[ref_id],Table4[euros])</f>
-        <v>23.11</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="0"/>
-        <v>2218.56</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="34" t="s">
         <v>250</v>
       </c>
@@ -19201,16 +19167,8 @@
       <c r="D27" s="37">
         <v>46203</v>
       </c>
-      <c r="E27">
-        <f>_xlfn.XLOOKUP(B27,Table4[ref_id],Table4[euros])</f>
-        <v>18.52</v>
-      </c>
-      <c r="F27">
-        <f t="shared" si="0"/>
-        <v>3704</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="34" t="s">
         <v>251</v>
       </c>
@@ -19220,16 +19178,8 @@
       <c r="D28" s="37">
         <v>46203</v>
       </c>
-      <c r="E28">
-        <f>_xlfn.XLOOKUP(B28,Table4[ref_id],Table4[euros])</f>
-        <v>18.36</v>
-      </c>
-      <c r="F28">
-        <f t="shared" si="0"/>
-        <v>1762.56</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="34" t="s">
         <v>521</v>
       </c>
@@ -19239,16 +19189,8 @@
       <c r="D29" s="37">
         <v>46203</v>
       </c>
-      <c r="E29">
-        <f>_xlfn.XLOOKUP(B29,Table4[ref_id],Table4[euros])</f>
-        <v>16.78</v>
-      </c>
-      <c r="F29">
-        <f t="shared" si="0"/>
-        <v>3221.76</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="34" t="s">
         <v>279</v>
       </c>
@@ -19258,16 +19200,8 @@
       <c r="D30" s="37">
         <v>46203</v>
       </c>
-      <c r="E30">
-        <f>_xlfn.XLOOKUP(B30,Table4[ref_id],Table4[euros])</f>
-        <v>16.850000000000001</v>
-      </c>
-      <c r="F30">
-        <f t="shared" si="0"/>
-        <v>3370.0000000000005</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="34" t="s">
         <v>286</v>
       </c>
@@ -19277,16 +19211,8 @@
       <c r="D31" s="37">
         <v>46203</v>
       </c>
-      <c r="E31">
-        <f>_xlfn.XLOOKUP(B31,Table4[ref_id],Table4[euros])</f>
-        <v>17.73</v>
-      </c>
-      <c r="F31">
-        <f t="shared" si="0"/>
-        <v>3546</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="34" t="s">
         <v>291</v>
       </c>
@@ -19296,16 +19222,8 @@
       <c r="D32" s="37">
         <v>46203</v>
       </c>
-      <c r="E32">
-        <f>_xlfn.XLOOKUP(B32,Table4[ref_id],Table4[euros])</f>
-        <v>21</v>
-      </c>
-      <c r="F32">
-        <f t="shared" si="0"/>
-        <v>2520</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="34" t="s">
         <v>297</v>
       </c>
@@ -19315,16 +19233,8 @@
       <c r="D33" s="37">
         <v>46203</v>
       </c>
-      <c r="E33">
-        <f>_xlfn.XLOOKUP(B33,Table4[ref_id],Table4[euros])</f>
-        <v>21.88</v>
-      </c>
-      <c r="F33">
-        <f t="shared" si="0"/>
-        <v>8752</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="34" t="s">
         <v>300</v>
       </c>
@@ -19334,16 +19244,8 @@
       <c r="D34" s="37">
         <v>46203</v>
       </c>
-      <c r="E34">
-        <f>_xlfn.XLOOKUP(B34,Table4[ref_id],Table4[euros])</f>
-        <v>19.8</v>
-      </c>
-      <c r="F34">
-        <f t="shared" si="0"/>
-        <v>4752</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="34" t="s">
         <v>308</v>
       </c>
@@ -19353,16 +19255,8 @@
       <c r="D35" s="37">
         <v>46203</v>
       </c>
-      <c r="E35">
-        <f>_xlfn.XLOOKUP(B35,Table4[ref_id],Table4[euros])</f>
-        <v>22.97</v>
-      </c>
-      <c r="F35">
-        <f t="shared" si="0"/>
-        <v>2205.12</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="34" t="s">
         <v>310</v>
       </c>
@@ -19372,16 +19266,8 @@
       <c r="D36" s="37">
         <v>46203</v>
       </c>
-      <c r="E36">
-        <f>_xlfn.XLOOKUP(B36,Table4[ref_id],Table4[euros])</f>
-        <v>32.17</v>
-      </c>
-      <c r="F36">
-        <f t="shared" si="0"/>
-        <v>3860.4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="34" t="s">
         <v>513</v>
       </c>
@@ -19391,16 +19277,8 @@
       <c r="D37" s="37">
         <v>46203</v>
       </c>
-      <c r="E37">
-        <f>_xlfn.XLOOKUP(B37,Table4[ref_id],Table4[euros])</f>
-        <v>12.05</v>
-      </c>
-      <c r="F37">
-        <f t="shared" si="0"/>
-        <v>3084.8</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="34" t="s">
         <v>312</v>
       </c>
@@ -19410,16 +19288,8 @@
       <c r="D38" s="37">
         <v>46203</v>
       </c>
-      <c r="E38">
-        <f>_xlfn.XLOOKUP(B38,Table4[ref_id],Table4[euros])</f>
-        <v>15.16</v>
-      </c>
-      <c r="F38">
-        <f t="shared" si="0"/>
-        <v>2364.96</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="34" t="s">
         <v>327</v>
       </c>
@@ -19429,16 +19299,8 @@
       <c r="D39" s="37">
         <v>46203</v>
       </c>
-      <c r="E39">
-        <f>_xlfn.XLOOKUP(B39,Table4[ref_id],Table4[euros])</f>
-        <v>8.98</v>
-      </c>
-      <c r="F39">
-        <f t="shared" si="0"/>
-        <v>1077.6000000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="34" t="s">
         <v>358</v>
       </c>
@@ -19448,16 +19310,8 @@
       <c r="D40" s="37">
         <v>46203</v>
       </c>
-      <c r="E40">
-        <f>_xlfn.XLOOKUP(B40,Table4[ref_id],Table4[euros])</f>
-        <v>32.32</v>
-      </c>
-      <c r="F40">
-        <f t="shared" si="0"/>
-        <v>9308.16</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="34" t="s">
         <v>359</v>
       </c>
@@ -19467,16 +19321,8 @@
       <c r="D41" s="37">
         <v>46203</v>
       </c>
-      <c r="E41">
-        <f>_xlfn.XLOOKUP(B41,Table4[ref_id],Table4[euros])</f>
-        <v>30.59</v>
-      </c>
-      <c r="F41">
-        <f t="shared" si="0"/>
-        <v>4404.96</v>
-      </c>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="34" t="s">
         <v>361</v>
       </c>
@@ -19486,16 +19332,8 @@
       <c r="D42" s="37">
         <v>46203</v>
       </c>
-      <c r="E42">
-        <f>_xlfn.XLOOKUP(B42,Table4[ref_id],Table4[euros])</f>
-        <v>31.03</v>
-      </c>
-      <c r="F42">
-        <f t="shared" si="0"/>
-        <v>4468.32</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="34" t="s">
         <v>280</v>
       </c>
@@ -19505,16 +19343,8 @@
       <c r="D43" s="37">
         <v>46203</v>
       </c>
-      <c r="E43">
-        <f>_xlfn.XLOOKUP(B43,Table4[ref_id],Table4[euros])</f>
-        <v>22.94</v>
-      </c>
-      <c r="F43">
-        <f t="shared" si="0"/>
-        <v>5505.6</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="34" t="s">
         <v>365</v>
       </c>
@@ -19524,16 +19354,8 @@
       <c r="D44" s="37">
         <v>46175</v>
       </c>
-      <c r="E44">
-        <f>_xlfn.XLOOKUP(B44,Table4[ref_id],Table4[euros])</f>
-        <v>26.32</v>
-      </c>
-      <c r="F44">
-        <f t="shared" si="0"/>
-        <v>4632.32</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="34" t="s">
         <v>369</v>
       </c>
@@ -19543,16 +19365,8 @@
       <c r="D45" s="37">
         <v>46203</v>
       </c>
-      <c r="E45">
-        <f>_xlfn.XLOOKUP(B45,Table4[ref_id],Table4[euros])</f>
-        <v>26.32</v>
-      </c>
-      <c r="F45">
-        <f t="shared" si="0"/>
-        <v>2316.16</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="34" t="s">
         <v>370</v>
       </c>
@@ -19562,16 +19376,8 @@
       <c r="D46" s="37">
         <v>46177</v>
       </c>
-      <c r="E46">
-        <f>_xlfn.XLOOKUP(B46,Table4[ref_id],Table4[euros])</f>
-        <v>23.46</v>
-      </c>
-      <c r="F46">
-        <f t="shared" si="0"/>
-        <v>2064.48</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="34" t="s">
         <v>371</v>
       </c>
@@ -19581,16 +19387,8 @@
       <c r="D47" s="37">
         <v>46177</v>
       </c>
-      <c r="E47">
-        <f>_xlfn.XLOOKUP(B47,Table4[ref_id],Table4[euros])</f>
-        <v>33.42</v>
-      </c>
-      <c r="F47">
-        <f t="shared" si="0"/>
-        <v>11763.84</v>
-      </c>
-    </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="34" t="s">
         <v>301</v>
       </c>
@@ -19600,16 +19398,8 @@
       <c r="D48" s="37">
         <v>46177</v>
       </c>
-      <c r="E48">
-        <f>_xlfn.XLOOKUP(B48,Table4[ref_id],Table4[euros])</f>
-        <v>35.36</v>
-      </c>
-      <c r="F48">
-        <f t="shared" si="0"/>
-        <v>6223.36</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="34" t="s">
         <v>313</v>
       </c>
@@ -19619,16 +19409,8 @@
       <c r="D49" s="37">
         <v>46177</v>
       </c>
-      <c r="E49">
-        <f>_xlfn.XLOOKUP(B49,Table4[ref_id],Table4[euros])</f>
-        <v>17.22</v>
-      </c>
-      <c r="F49">
-        <f t="shared" si="0"/>
-        <v>3306.24</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="34" t="s">
         <v>253</v>
       </c>
@@ -19638,16 +19420,8 @@
       <c r="D50" s="37">
         <v>46177</v>
       </c>
-      <c r="E50">
-        <f>_xlfn.XLOOKUP(B50,Table4[ref_id],Table4[euros])</f>
-        <v>19.37</v>
-      </c>
-      <c r="F50">
-        <f t="shared" si="0"/>
-        <v>1220.3100000000002</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="34" t="s">
         <v>377</v>
       </c>
@@ -19657,16 +19431,8 @@
       <c r="D51" s="37">
         <v>46177</v>
       </c>
-      <c r="E51">
-        <f>_xlfn.XLOOKUP(B51,Table4[ref_id],Table4[euros])</f>
-        <v>25.39</v>
-      </c>
-      <c r="F51">
-        <f t="shared" si="0"/>
-        <v>4468.6400000000003</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B52" s="34" t="s">
         <v>314</v>
       </c>
@@ -19676,16 +19442,8 @@
       <c r="D52" s="37">
         <v>46177</v>
       </c>
-      <c r="E52">
-        <f>_xlfn.XLOOKUP(B52,Table4[ref_id],Table4[euros])</f>
-        <v>13.65</v>
-      </c>
-      <c r="F52">
-        <f t="shared" si="0"/>
-        <v>3439.8</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B53" s="34" t="s">
         <v>236</v>
       </c>
@@ -19695,16 +19453,8 @@
       <c r="D53" s="37">
         <v>46195</v>
       </c>
-      <c r="E53">
-        <f>_xlfn.XLOOKUP(B53,Table4[ref_id],Table4[euros])</f>
-        <v>22.36</v>
-      </c>
-      <c r="F53">
-        <f t="shared" ref="F53:F86" si="1">E53*C53</f>
-        <v>4293.12</v>
-      </c>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B54" s="37" t="s">
         <v>241</v>
       </c>
@@ -19714,16 +19464,8 @@
       <c r="D54" s="37">
         <v>46203</v>
       </c>
-      <c r="E54">
-        <f>_xlfn.XLOOKUP(B54,Table4[ref_id],Table4[euros])</f>
-        <v>22.79</v>
-      </c>
-      <c r="F54">
-        <f t="shared" si="1"/>
-        <v>2187.84</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B55" s="37" t="s">
         <v>254</v>
       </c>
@@ -19733,265 +19475,153 @@
       <c r="D55" s="37">
         <v>46203</v>
       </c>
-      <c r="E55">
-        <f>_xlfn.XLOOKUP(B55,Table4[ref_id],Table4[euros])</f>
-        <v>23</v>
-      </c>
-      <c r="F55">
-        <f t="shared" si="1"/>
-        <v>1449</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B56" s="37" t="s">
-        <v>379</v>
+        <v>255</v>
       </c>
       <c r="C56" s="54">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="D56" s="37">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B57" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="C57" s="54">
+        <v>3808</v>
+      </c>
+      <c r="D57" s="37">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B58" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="C58" s="54">
+        <v>3060</v>
+      </c>
+      <c r="D58" s="37">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B59" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="C59" s="54">
+        <v>96</v>
+      </c>
+      <c r="D59" s="37">
         <v>46203</v>
       </c>
-      <c r="E56">
-        <f>_xlfn.XLOOKUP(B56,Table4[ref_id],Table4[euros])</f>
-        <v>17.02</v>
-      </c>
-      <c r="F56">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B57" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="C57" s="54">
-        <v>260</v>
-      </c>
-      <c r="D57" s="37">
-        <v>46202</v>
-      </c>
-      <c r="E57">
-        <f>_xlfn.XLOOKUP(B57,Table4[ref_id],Table4[euros])</f>
-        <v>19.59</v>
-      </c>
-      <c r="F57">
-        <f t="shared" si="1"/>
-        <v>5093.3999999999996</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B58" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="C58" s="54">
-        <v>3808</v>
-      </c>
-      <c r="D58" s="37">
-        <v>46178</v>
-      </c>
-      <c r="E58">
-        <f>_xlfn.XLOOKUP(B58,Table4[ref_id],Table4[euros])</f>
-        <v>22.6</v>
-      </c>
-      <c r="F58">
-        <f t="shared" si="1"/>
-        <v>86060.800000000003</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B59" s="37" t="s">
-        <v>376</v>
-      </c>
-      <c r="C59" s="54">
-        <v>3060</v>
-      </c>
-      <c r="D59" s="37">
-        <v>46186</v>
-      </c>
-      <c r="E59">
-        <f>_xlfn.XLOOKUP(B59,Table4[ref_id],Table4[euros])</f>
-        <v>28.96</v>
-      </c>
-      <c r="F59">
-        <f t="shared" si="1"/>
-        <v>88617.600000000006</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B60" s="37" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="C60" s="54">
         <v>96</v>
       </c>
       <c r="D60" s="37">
-        <v>46203</v>
-      </c>
-      <c r="E60">
-        <f>_xlfn.XLOOKUP(B60,Table4[ref_id],Table4[euros])</f>
-        <v>33.74</v>
-      </c>
-      <c r="F60">
-        <f t="shared" si="1"/>
-        <v>3239.04</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.35">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B61" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C61" s="54">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="D61" s="37">
         <v>46177</v>
       </c>
-      <c r="E61">
-        <f>_xlfn.XLOOKUP(B61,Table4[ref_id],Table4[euros])</f>
-        <v>40.64</v>
-      </c>
-      <c r="F61">
-        <f t="shared" si="1"/>
-        <v>3901.44</v>
-      </c>
-    </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B62" s="37" t="s">
-        <v>305</v>
+        <v>261</v>
       </c>
       <c r="C62" s="54">
-        <v>192</v>
+        <v>64</v>
       </c>
       <c r="D62" s="37">
         <v>46177</v>
       </c>
-      <c r="E62">
-        <f>_xlfn.XLOOKUP(B62,Table4[ref_id],Table4[euros])</f>
-        <v>30.94</v>
-      </c>
-      <c r="F62">
-        <f t="shared" si="1"/>
-        <v>5940.4800000000005</v>
-      </c>
-    </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B63" s="37" t="s">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c r="C63" s="54">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D63" s="37">
-        <v>46177</v>
-      </c>
-      <c r="E63">
-        <f>_xlfn.XLOOKUP(B63,Table4[ref_id],Table4[euros])</f>
-        <v>40.479999999999997</v>
-      </c>
-      <c r="F63">
-        <f t="shared" si="1"/>
-        <v>2590.7199999999998</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B64" s="37" t="s">
-        <v>328</v>
+        <v>265</v>
       </c>
       <c r="C64" s="54">
-        <v>96</v>
+        <v>256</v>
       </c>
       <c r="D64" s="37">
-        <v>46175</v>
-      </c>
-      <c r="E64">
-        <f>_xlfn.XLOOKUP(B64,Table4[ref_id],Table4[euros])</f>
-        <v>37.94</v>
-      </c>
-      <c r="F64">
-        <f t="shared" si="1"/>
-        <v>3642.24</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.35">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B65" s="37" t="s">
-        <v>265</v>
+        <v>352</v>
       </c>
       <c r="C65" s="54">
-        <v>256</v>
+        <v>600</v>
       </c>
       <c r="D65" s="37">
         <v>46203</v>
       </c>
-      <c r="E65">
-        <f>_xlfn.XLOOKUP(B65,Table4[ref_id],Table4[euros])</f>
-        <v>6.71</v>
-      </c>
-      <c r="F65">
-        <f t="shared" si="1"/>
-        <v>1717.76</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B66" s="37" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="C66" s="54">
-        <v>600</v>
+        <v>216</v>
       </c>
       <c r="D66" s="37">
         <v>46203</v>
       </c>
-      <c r="E66">
-        <f>_xlfn.XLOOKUP(B66,Table4[ref_id],Table4[euros])</f>
-        <v>11.34</v>
-      </c>
-      <c r="F66">
-        <f t="shared" si="1"/>
-        <v>6804</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B67" s="37" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C67" s="54">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="D67" s="37">
         <v>46203</v>
       </c>
-      <c r="E67">
-        <f>_xlfn.XLOOKUP(B67,Table4[ref_id],Table4[euros])</f>
-        <v>17.28</v>
-      </c>
-      <c r="F67">
-        <f t="shared" si="1"/>
-        <v>3732.4800000000005</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B68" s="37" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="C68" s="54">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D68" s="37">
         <v>46203</v>
       </c>
-      <c r="E68">
-        <f>_xlfn.XLOOKUP(B68,Table4[ref_id],Table4[euros])</f>
-        <v>16.489999999999998</v>
-      </c>
-      <c r="F68">
-        <f t="shared" si="1"/>
-        <v>1780.9199999999998</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B69" s="37" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C69" s="54">
         <v>72</v>
@@ -19999,94 +19629,54 @@
       <c r="D69" s="37">
         <v>46203</v>
       </c>
-      <c r="E69">
-        <f>_xlfn.XLOOKUP(B69,Table4[ref_id],Table4[euros])</f>
-        <v>32.81</v>
-      </c>
-      <c r="F69">
-        <f t="shared" si="1"/>
-        <v>2362.3200000000002</v>
-      </c>
-    </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B70" s="37" t="s">
-        <v>364</v>
+        <v>321</v>
       </c>
       <c r="C70" s="54">
-        <v>72</v>
+        <v>360</v>
       </c>
       <c r="D70" s="37">
         <v>46203</v>
       </c>
-      <c r="E70">
-        <f>_xlfn.XLOOKUP(B70,Table4[ref_id],Table4[euros])</f>
-        <v>32.35</v>
-      </c>
-      <c r="F70">
-        <f t="shared" si="1"/>
-        <v>2329.2000000000003</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B71" s="37" t="s">
-        <v>321</v>
+        <v>375</v>
       </c>
       <c r="C71" s="54">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="D71" s="37">
         <v>46203</v>
       </c>
-      <c r="E71">
-        <f>_xlfn.XLOOKUP(B71,Table4[ref_id],Table4[euros])</f>
-        <v>30.98</v>
-      </c>
-      <c r="F71">
-        <f t="shared" si="1"/>
-        <v>11152.8</v>
-      </c>
-    </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B72" s="37" t="s">
-        <v>375</v>
+        <v>307</v>
       </c>
       <c r="C72" s="54">
-        <v>384</v>
+        <v>192</v>
       </c>
       <c r="D72" s="37">
         <v>46203</v>
       </c>
-      <c r="E72">
-        <f>_xlfn.XLOOKUP(B72,Table4[ref_id],Table4[euros])</f>
-        <v>15.68</v>
-      </c>
-      <c r="F72">
-        <f t="shared" si="1"/>
-        <v>6021.12</v>
-      </c>
-    </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B73" s="37" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="C73" s="54">
-        <v>192</v>
+        <v>63</v>
       </c>
       <c r="D73" s="37">
         <v>46203</v>
       </c>
-      <c r="E73">
-        <f>_xlfn.XLOOKUP(B73,Table4[ref_id],Table4[euros])</f>
-        <v>30.94</v>
-      </c>
-      <c r="F73">
-        <f t="shared" si="1"/>
-        <v>5940.4800000000005</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B74" s="37" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="C74" s="54">
         <v>63</v>
@@ -20094,18 +19684,10 @@
       <c r="D74" s="37">
         <v>46203</v>
       </c>
-      <c r="E74">
-        <f>_xlfn.XLOOKUP(B74,Table4[ref_id],Table4[euros])</f>
-        <v>14.71</v>
-      </c>
-      <c r="F74">
-        <f t="shared" si="1"/>
-        <v>926.73</v>
-      </c>
-    </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B75" s="37" t="s">
-        <v>282</v>
+        <v>333</v>
       </c>
       <c r="C75" s="54">
         <v>63</v>
@@ -20113,222 +19695,115 @@
       <c r="D75" s="37">
         <v>46203</v>
       </c>
-      <c r="E75">
-        <f>_xlfn.XLOOKUP(B75,Table4[ref_id],Table4[euros])</f>
-        <v>16.309999999999999</v>
-      </c>
-      <c r="F75">
-        <f t="shared" si="1"/>
-        <v>1027.53</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B76" s="37" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="C76" s="54">
-        <v>63</v>
+        <v>1276</v>
       </c>
       <c r="D76" s="37">
         <v>46203</v>
       </c>
-      <c r="E76">
-        <f>_xlfn.XLOOKUP(B76,Table4[ref_id],Table4[euros])</f>
-        <v>16.93</v>
-      </c>
-      <c r="F76">
-        <f t="shared" si="1"/>
-        <v>1066.5899999999999</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B77" s="37" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C77" s="54">
-        <v>1276</v>
+        <v>768</v>
       </c>
       <c r="D77" s="37">
         <v>46203</v>
       </c>
-      <c r="E77">
-        <f>_xlfn.XLOOKUP(B77,Table4[ref_id],Table4[euros])</f>
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="F77">
-        <f t="shared" si="1"/>
-        <v>11228.800000000001</v>
-      </c>
-    </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B78" s="37" t="s">
-        <v>326</v>
+        <v>296</v>
       </c>
       <c r="C78" s="54">
-        <v>768</v>
+        <v>896</v>
       </c>
       <c r="D78" s="37">
         <v>46203</v>
       </c>
-      <c r="E78">
-        <f>_xlfn.XLOOKUP(B78,Table4[ref_id],Table4[euros])</f>
-        <v>9.34</v>
-      </c>
-      <c r="F78">
-        <f t="shared" si="1"/>
-        <v>7173.12</v>
-      </c>
-    </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B79" s="37" t="s">
-        <v>296</v>
+        <v>329</v>
       </c>
       <c r="C79" s="54">
-        <v>896</v>
+        <v>256</v>
       </c>
       <c r="D79" s="37">
         <v>46203</v>
       </c>
-      <c r="E79">
-        <f>_xlfn.XLOOKUP(B79,Table4[ref_id],Table4[euros])</f>
-        <v>8.9700000000000006</v>
-      </c>
-      <c r="F79">
-        <f t="shared" si="1"/>
-        <v>8037.1200000000008</v>
-      </c>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B80" s="37" t="s">
-        <v>329</v>
+        <v>223</v>
       </c>
       <c r="C80" s="54">
-        <v>256</v>
+        <v>88</v>
       </c>
       <c r="D80" s="37">
         <v>46203</v>
       </c>
-      <c r="E80">
-        <f>_xlfn.XLOOKUP(B80,Table4[ref_id],Table4[euros])</f>
-        <v>8.9700000000000006</v>
-      </c>
-      <c r="F80">
-        <f t="shared" si="1"/>
-        <v>2296.3200000000002</v>
-      </c>
-    </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B81" s="37" t="s">
-        <v>223</v>
+        <v>330</v>
       </c>
       <c r="C81" s="54">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="D81" s="37">
         <v>46203</v>
       </c>
-      <c r="E81">
-        <f>_xlfn.XLOOKUP(B81,Table4[ref_id],Table4[euros])</f>
-        <v>23.46</v>
-      </c>
-      <c r="F81">
-        <f t="shared" si="1"/>
-        <v>2064.48</v>
-      </c>
-    </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B82" s="37" t="s">
-        <v>330</v>
+        <v>226</v>
       </c>
       <c r="C82" s="54">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="D82" s="37">
         <v>46203</v>
       </c>
-      <c r="E82">
-        <f>_xlfn.XLOOKUP(B82,Table4[ref_id],Table4[euros])</f>
-        <v>10.06</v>
-      </c>
-      <c r="F82">
-        <f t="shared" si="1"/>
-        <v>1126.72</v>
-      </c>
-    </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="83" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B83" s="37" t="s">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="C83" s="54">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D83" s="37">
         <v>46203</v>
       </c>
-      <c r="E83">
-        <f>_xlfn.XLOOKUP(B83,Table4[ref_id],Table4[euros])</f>
-        <v>21.61</v>
-      </c>
-      <c r="F83">
-        <f t="shared" si="1"/>
-        <v>1815.24</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B84" s="37" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="C84" s="54">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="D84" s="37">
         <v>46203</v>
       </c>
-      <c r="E84">
-        <f>_xlfn.XLOOKUP(B84,Table4[ref_id],Table4[euros])</f>
-        <v>25.29</v>
-      </c>
-      <c r="F84">
-        <f t="shared" si="1"/>
-        <v>1820.8799999999999</v>
-      </c>
-    </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B85" s="37" t="s">
-        <v>288</v>
+        <v>225</v>
       </c>
       <c r="C85" s="54">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="D85" s="37">
         <v>46203</v>
-      </c>
-      <c r="E85">
-        <f>_xlfn.XLOOKUP(B85,Table4[ref_id],Table4[euros])</f>
-        <v>37.49</v>
-      </c>
-      <c r="F85">
-        <f t="shared" si="1"/>
-        <v>1799.52</v>
-      </c>
-    </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B86" s="37" t="s">
-        <v>225</v>
-      </c>
-      <c r="C86" s="54">
-        <v>84</v>
-      </c>
-      <c r="D86" s="37">
-        <v>46203</v>
-      </c>
-      <c r="E86">
-        <f>_xlfn.XLOOKUP(B86,Table4[ref_id],Table4[euros])</f>
-        <v>21</v>
-      </c>
-      <c r="F86">
-        <f t="shared" si="1"/>
-        <v>1764</v>
       </c>
     </row>
   </sheetData>
@@ -20337,6 +19812,7 @@
     <mergeCell ref="B1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Inputs_EmpresaX.xlsx
+++ b/Inputs_EmpresaX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kaizen\Documents\tese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C72EABB-EEF4-4113-AF00-641176C2A83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E759BB-FC63-4BE4-B76D-641271111F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Inputs_EmpresaX.xlsx
+++ b/Inputs_EmpresaX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kaizen\Documents\tese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E759BB-FC63-4BE4-B76D-641271111F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B12E16C-4855-47FC-B1D2-AFB9806C9D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2891,6 +2891,18 @@
     <xf numFmtId="1" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2900,16 +2912,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2927,33 +2939,11 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <font>
         <b val="0"/>
@@ -3692,26 +3682,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A2E0425D-8D3D-4317-A507-ADC777C31517}" name="Table4" displayName="Table4" ref="A4:Q192" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A2E0425D-8D3D-4317-A507-ADC777C31517}" name="Table4" displayName="Table4" ref="A4:Q192" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18" tableBorderDxfId="17">
   <autoFilter ref="A4:Q192" xr:uid="{A2E0425D-8D3D-4317-A507-ADC777C31517}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{26D481BD-1A66-4F75-A5DB-835BDEAD35EC}" name="ref_id" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{AF3D888D-29CC-4818-9F37-35E1C095FEBC}" name="nome" dataDxfId="16"/>
-    <tableColumn id="21" xr3:uid="{A36D18E5-0E2F-48D2-A9EA-1667409CF7FA}" name="Unid_caixa" dataDxfId="15"/>
-    <tableColumn id="19" xr3:uid="{901BF69A-B9CB-436F-8A73-E52E627A4C44}" name="nao_produzir_segunda" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{73E06642-D2DC-4B3F-B7AE-6A99CF0B73CD}" name="família" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{47F7E5B0-45A6-4E01-8304-DD4D19A9E24E}" name="ativa" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{E576D14B-BDA0-4CA6-B2F4-097D5C1CE99B}" name="pode_L1" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{B29DBEC4-DD50-4914-98AC-30F025559FDC}" name="tempo_L1_prod_min (cadência de L1)" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{14DD02B2-C00E-494B-A8F3-3FFAE31BC4FB}" name="operadores_nec_L1_acab" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{89492EE9-DE84-43EE-B12E-2605FE3EAD79}" name="operadores_nec_L1_prod" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{780BF028-7B4E-42E1-B807-EDB2FB22CEE7}" name="pode_L2" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{FD12F15B-F3BE-48A4-B186-794E71F468D8}" name="tempo_L2_prod_min (cadência de L2)" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{2B695F9C-3774-41DD-8FE4-AF094E98B022}" name="tempo_L2_acab_min (cadência de L2)" dataDxfId="5"/>
-    <tableColumn id="20" xr3:uid="{46C45284-5F2B-442A-A3EB-D66468126784}" name="operadores_nec_L2_acab" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{1453032D-3307-46D2-BB7E-3D55B4D2E43D}" name="operadores_nec_L2_prod" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{5009F860-773A-42AE-9780-72CCCE321658}" name="kg" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{3939DDEA-30DE-43D1-B600-33ECEC5CD680}" name="euros" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{26D481BD-1A66-4F75-A5DB-835BDEAD35EC}" name="ref_id" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{AF3D888D-29CC-4818-9F37-35E1C095FEBC}" name="nome" dataDxfId="15"/>
+    <tableColumn id="21" xr3:uid="{A36D18E5-0E2F-48D2-A9EA-1667409CF7FA}" name="Unid_caixa" dataDxfId="14"/>
+    <tableColumn id="19" xr3:uid="{901BF69A-B9CB-436F-8A73-E52E627A4C44}" name="nao_produzir_segunda" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{73E06642-D2DC-4B3F-B7AE-6A99CF0B73CD}" name="família" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{47F7E5B0-45A6-4E01-8304-DD4D19A9E24E}" name="ativa" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{E576D14B-BDA0-4CA6-B2F4-097D5C1CE99B}" name="pode_L1" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{B29DBEC4-DD50-4914-98AC-30F025559FDC}" name="tempo_L1_prod_min (cadência de L1)" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{14DD02B2-C00E-494B-A8F3-3FFAE31BC4FB}" name="operadores_nec_L1_acab" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{89492EE9-DE84-43EE-B12E-2605FE3EAD79}" name="operadores_nec_L1_prod" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{780BF028-7B4E-42E1-B807-EDB2FB22CEE7}" name="pode_L2" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{FD12F15B-F3BE-48A4-B186-794E71F468D8}" name="tempo_L2_prod_min (cadência de L2)" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{2B695F9C-3774-41DD-8FE4-AF094E98B022}" name="tempo_L2_acab_min (cadência de L2)" dataDxfId="4"/>
+    <tableColumn id="20" xr3:uid="{46C45284-5F2B-442A-A3EB-D66468126784}" name="operadores_nec_L2_acab" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{1453032D-3307-46D2-BB7E-3D55B4D2E43D}" name="operadores_nec_L2_prod" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{5009F860-773A-42AE-9780-72CCCE321658}" name="kg" dataDxfId="1"/>
+    <tableColumn id="18" xr3:uid="{3939DDEA-30DE-43D1-B600-33ECEC5CD680}" name="euros" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4058,11 +4048,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -4094,11 +4084,11 @@
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
@@ -4131,11 +4121,11 @@
       <c r="C9" s="3"/>
     </row>
     <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="58" t="s">
+      <c r="A11" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
     </row>
     <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
@@ -4159,11 +4149,11 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="58" t="s">
+      <c r="A15" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="63"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
@@ -4245,11 +4235,11 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="58" t="s">
+      <c r="A24" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
+      <c r="B24" s="63"/>
+      <c r="C24" s="63"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
@@ -4329,11 +4319,11 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="58" t="s">
+      <c r="A33" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="59"/>
-      <c r="C33" s="59"/>
+      <c r="B33" s="63"/>
+      <c r="C33" s="63"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
@@ -4348,69 +4338,74 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="66" t="s">
+      <c r="A37" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="59"/>
-      <c r="C37" s="59"/>
+      <c r="B37" s="63"/>
+      <c r="C37" s="63"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="65" t="s">
+      <c r="A39" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="62"/>
-      <c r="C39" s="62"/>
+      <c r="B39" s="65"/>
+      <c r="C39" s="65"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="64" t="s">
+      <c r="A40" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="62"/>
-      <c r="C40" s="62"/>
+      <c r="B40" s="65"/>
+      <c r="C40" s="65"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="64"/>
-      <c r="B41" s="62"/>
-      <c r="C41" s="62"/>
+      <c r="A41" s="68"/>
+      <c r="B41" s="65"/>
+      <c r="C41" s="65"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="63" t="s">
+      <c r="A42" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="62"/>
-      <c r="C42" s="62"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="61" t="s">
+      <c r="A43" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="62"/>
-      <c r="C43" s="62"/>
+      <c r="B43" s="65"/>
+      <c r="C43" s="65"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="64" t="s">
+      <c r="A44" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="62"/>
-      <c r="C44" s="62"/>
+      <c r="B44" s="65"/>
+      <c r="C44" s="65"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="60"/>
-      <c r="B45" s="59"/>
-      <c r="C45" s="59"/>
+      <c r="A45" s="62"/>
+      <c r="B45" s="63"/>
+      <c r="C45" s="63"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="60"/>
-      <c r="B46" s="59"/>
-      <c r="C46" s="59"/>
+      <c r="A46" s="62"/>
+      <c r="B46" s="63"/>
+      <c r="C46" s="63"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="60"/>
-      <c r="B47" s="59"/>
-      <c r="C47" s="59"/>
+      <c r="A47" s="62"/>
+      <c r="B47" s="63"/>
+      <c r="C47" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A46:C46"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A43:C43"/>
@@ -4422,11 +4417,6 @@
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A46:C46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4458,44 +4448,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
     </row>
     <row r="2" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
     </row>
     <row r="4" spans="1:17" ht="31" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
@@ -12899,9 +12889,11 @@
         <v>22</v>
       </c>
       <c r="L158" s="45">
-        <v>76</v>
-      </c>
-      <c r="M158" s="45"/>
+        <v>1824</v>
+      </c>
+      <c r="M158" s="45">
+        <v>1824</v>
+      </c>
       <c r="N158" s="45">
         <v>2</v>
       </c>
@@ -14757,109 +14749,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56"/>
-      <c r="AA1" s="56"/>
-      <c r="AB1" s="56"/>
-      <c r="AC1" s="56"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+      <c r="X1" s="60"/>
+      <c r="Y1" s="60"/>
+      <c r="Z1" s="60"/>
+      <c r="AA1" s="60"/>
+      <c r="AB1" s="60"/>
+      <c r="AC1" s="60"/>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="59" t="s">
         <v>400</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
-      <c r="V2" s="56"/>
-      <c r="W2" s="56"/>
-      <c r="X2" s="56"/>
-      <c r="Y2" s="56"/>
-      <c r="Z2" s="56"/>
-      <c r="AA2" s="56"/>
-      <c r="AB2" s="56"/>
-      <c r="AC2" s="56"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
     </row>
     <row r="3" spans="1:38" ht="32" x14ac:dyDescent="0.7">
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="72" t="s">
         <v>511</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
-      <c r="V3" s="68"/>
-      <c r="W3" s="68"/>
-      <c r="X3" s="68"/>
-      <c r="Y3" s="68"/>
-      <c r="Z3" s="68"/>
-      <c r="AA3" s="68"/>
-      <c r="AB3" s="68"/>
-      <c r="AC3" s="68"/>
-      <c r="AD3" s="68"/>
-      <c r="AE3" s="68"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="68"/>
-      <c r="AJ3" s="68"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="72"/>
+      <c r="T3" s="72"/>
+      <c r="U3" s="72"/>
+      <c r="V3" s="72"/>
+      <c r="W3" s="72"/>
+      <c r="X3" s="72"/>
+      <c r="Y3" s="72"/>
+      <c r="Z3" s="72"/>
+      <c r="AA3" s="72"/>
+      <c r="AB3" s="72"/>
+      <c r="AC3" s="72"/>
+      <c r="AD3" s="72"/>
+      <c r="AE3" s="72"/>
+      <c r="AF3" s="72"/>
+      <c r="AG3" s="72"/>
+      <c r="AH3" s="72"/>
+      <c r="AI3" s="72"/>
+      <c r="AJ3" s="72"/>
     </row>
     <row r="4" spans="1:38" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
@@ -18864,18 +18856,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
     </row>
     <row r="2" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="59" t="s">
         <v>404</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
     </row>
     <row r="4" spans="2:8" ht="45" x14ac:dyDescent="0.35">
       <c r="B4" s="35" t="s">
@@ -18887,13 +18879,13 @@
       <c r="D4" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="69" t="s">
+      <c r="F4" s="55" t="s">
         <v>528</v>
       </c>
-      <c r="G4" s="69" t="s">
+      <c r="G4" s="55" t="s">
         <v>529</v>
       </c>
-      <c r="H4" s="69" t="s">
+      <c r="H4" s="55" t="s">
         <v>530</v>
       </c>
     </row>
@@ -18907,13 +18899,13 @@
       <c r="D5" s="37">
         <v>46203</v>
       </c>
-      <c r="F5" s="70" t="s">
+      <c r="F5" s="56" t="s">
         <v>531</v>
       </c>
-      <c r="G5" s="71">
+      <c r="G5" s="57">
         <v>165.92526540126542</v>
       </c>
-      <c r="H5" s="72">
+      <c r="H5" s="58">
         <v>135</v>
       </c>
     </row>
@@ -18927,13 +18919,13 @@
       <c r="D6" s="37">
         <v>46203</v>
       </c>
-      <c r="F6" s="70" t="s">
+      <c r="F6" s="56" t="s">
         <v>532</v>
       </c>
-      <c r="G6" s="71">
+      <c r="G6" s="57">
         <v>241.03174325966435</v>
       </c>
-      <c r="H6" s="72">
+      <c r="H6" s="58">
         <v>135</v>
       </c>
     </row>

--- a/Inputs_EmpresaX.xlsx
+++ b/Inputs_EmpresaX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kaizen\Documents\tese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CDA9D7-4B7C-4417-A455-527527653BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30718A5A-D4BE-4D63-9783-99C9852C925F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1_ESTRUTURA" sheetId="2" state="hidden" r:id="rId1"/>
@@ -763,7 +763,7 @@
     <author>tc={C7364A66-A497-423F-B38F-AF51BEC19DB7}</author>
   </authors>
   <commentList>
-    <comment ref="J78" authorId="0" shapeId="0" xr:uid="{C7364A66-A497-423F-B38F-AF51BEC19DB7}">
+    <comment ref="M78" authorId="0" shapeId="0" xr:uid="{C7364A66-A497-423F-B38F-AF51BEC19DB7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -775,8 +775,30 @@
 </comments>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2549" uniqueCount="558">
   <si>
     <t>ESTRUTURA FÍSICA DO SISTEMA PRODUTIVO</t>
   </si>
@@ -2323,9 +2345,6 @@
     <t>DC804700C</t>
   </si>
   <si>
-    <t>DC804800R</t>
-  </si>
-  <si>
     <t>726504C - BOLO DE CHOCOLATE BROOKIE 650GR (4 UNID) CONGELADO</t>
   </si>
   <si>
@@ -2438,6 +2457,21 @@
   </si>
   <si>
     <t>DC011103</t>
+  </si>
+  <si>
+    <t>horas_prod</t>
+  </si>
+  <si>
+    <t>unid</t>
+  </si>
+  <si>
+    <t>tempo_total</t>
+  </si>
+  <si>
+    <t>Linha</t>
+  </si>
+  <si>
+    <t>DC804600R</t>
   </si>
 </sst>
 </file>
@@ -2823,7 +2857,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2992,6 +3026,18 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3028,20 +3074,35 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3067,30 +3128,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3850,7 +3887,7 @@
     <tableColumn id="17" xr3:uid="{1453032D-3307-46D2-BB7E-3D55B4D2E43D}" name="operadores_nec_L2_prod" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{5009F860-773A-42AE-9780-72CCCE321658}" name="kg" dataDxfId="5"/>
     <tableColumn id="18" xr3:uid="{3939DDEA-30DE-43D1-B600-33ECEC5CD680}" name="euros" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{F6639149-4E24-4A12-AD3E-4C337ED9850C}" name="abc" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{F6639149-4E24-4A12-AD3E-4C337ED9850C}" name="abc" dataDxfId="3">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4143,7 +4180,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="J78" dT="2026-05-21T13:53:57.62" personId="{DAA1B03B-E46D-4B86-913A-0A7B4214C9B3}" id="{C7364A66-A497-423F-B38F-AF51BEC19DB7}">
+  <threadedComment ref="M78" dT="2026-05-21T13:53:57.62" personId="{DAA1B03B-E46D-4B86-913A-0A7B4214C9B3}" id="{C7364A66-A497-423F-B38F-AF51BEC19DB7}">
     <text>900</text>
   </threadedComment>
 </ThreadedComments>
@@ -4199,11 +4236,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -4235,11 +4272,11 @@
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
@@ -4272,11 +4309,11 @@
       <c r="C9" s="3"/>
     </row>
     <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="62"/>
-      <c r="C11" s="62"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
     </row>
     <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
@@ -4300,11 +4337,11 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
@@ -4386,11 +4423,11 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="61" t="s">
+      <c r="A24" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
@@ -4470,11 +4507,11 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="61" t="s">
+      <c r="A33" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="62"/>
-      <c r="C33" s="62"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="66"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
@@ -4489,66 +4526,66 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="69" t="s">
+      <c r="A37" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="62"/>
-      <c r="C37" s="62"/>
+      <c r="B37" s="66"/>
+      <c r="C37" s="66"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="68" t="s">
+      <c r="A39" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="65"/>
-      <c r="C39" s="65"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="69"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="67" t="s">
+      <c r="A40" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="65"/>
-      <c r="C40" s="65"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="69"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="67"/>
-      <c r="B41" s="65"/>
-      <c r="C41" s="65"/>
+      <c r="A41" s="71"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="69"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="66" t="s">
+      <c r="A42" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="69"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="64" t="s">
+      <c r="A43" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="65"/>
-      <c r="C43" s="65"/>
+      <c r="B43" s="69"/>
+      <c r="C43" s="69"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="67" t="s">
+      <c r="A44" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="65"/>
-      <c r="C44" s="65"/>
+      <c r="B44" s="69"/>
+      <c r="C44" s="69"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="63"/>
-      <c r="B45" s="62"/>
-      <c r="C45" s="62"/>
+      <c r="A45" s="67"/>
+      <c r="B45" s="66"/>
+      <c r="C45" s="66"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="63"/>
-      <c r="B46" s="62"/>
-      <c r="C46" s="62"/>
+      <c r="A46" s="67"/>
+      <c r="B46" s="66"/>
+      <c r="C46" s="66"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="63"/>
-      <c r="B47" s="62"/>
-      <c r="C47" s="62"/>
+      <c r="A47" s="67"/>
+      <c r="B47" s="66"/>
+      <c r="C47" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -4599,44 +4636,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
     </row>
     <row r="2" spans="1:29" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="74"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="74"/>
+      <c r="Q2" s="74"/>
     </row>
     <row r="4" spans="1:29" ht="31" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
@@ -4649,7 +4686,7 @@
         <v>452</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>399</v>
@@ -4685,13 +4722,13 @@
         <v>451</v>
       </c>
       <c r="P4" s="39" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="Q4" s="39" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="R4" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -4746,15 +4783,15 @@
       <c r="Q5" s="46">
         <v>23.46</v>
       </c>
-      <c r="R5" s="72" t="str">
+      <c r="R5" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>A</v>
       </c>
-      <c r="AB5" s="73" t="s">
+      <c r="AB5" s="59" t="s">
         <v>260</v>
       </c>
-      <c r="AC5" s="73" t="s">
-        <v>534</v>
+      <c r="AC5" s="59" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -4809,15 +4846,15 @@
       <c r="Q6" s="46">
         <v>23.46</v>
       </c>
-      <c r="R6" s="72" t="str">
+      <c r="R6" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB6" s="74" t="s">
+      <c r="AB6" s="60" t="s">
         <v>376</v>
       </c>
-      <c r="AC6" s="74" t="s">
-        <v>534</v>
+      <c r="AC6" s="60" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -4872,15 +4909,15 @@
       <c r="Q7" s="46">
         <v>23.46</v>
       </c>
-      <c r="R7" s="72" t="str">
+      <c r="R7" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>A</v>
       </c>
-      <c r="AB7" s="73" t="s">
-        <v>536</v>
-      </c>
-      <c r="AC7" s="73" t="s">
-        <v>534</v>
+      <c r="AB7" s="59" t="s">
+        <v>535</v>
+      </c>
+      <c r="AC7" s="59" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -4935,15 +4972,15 @@
       <c r="Q8" s="48">
         <v>20.22</v>
       </c>
-      <c r="R8" s="72" t="str">
+      <c r="R8" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB8" s="74" t="s">
+      <c r="AB8" s="60" t="s">
         <v>325</v>
       </c>
-      <c r="AC8" s="74" t="s">
-        <v>534</v>
+      <c r="AC8" s="60" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -4998,15 +5035,15 @@
       <c r="Q9" s="48">
         <v>21</v>
       </c>
-      <c r="R9" s="72" t="str">
+      <c r="R9" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB9" s="73" t="s">
+      <c r="AB9" s="59" t="s">
         <v>296</v>
       </c>
-      <c r="AC9" s="73" t="s">
-        <v>534</v>
+      <c r="AC9" s="59" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -5061,15 +5098,15 @@
       <c r="Q10" s="48">
         <v>21.61</v>
       </c>
-      <c r="R10" s="72" t="str">
+      <c r="R10" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB10" s="74" t="s">
+      <c r="AB10" s="60" t="s">
         <v>242</v>
       </c>
-      <c r="AC10" s="74" t="s">
-        <v>534</v>
+      <c r="AC10" s="60" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -5124,15 +5161,15 @@
       <c r="Q11" s="48">
         <v>22.26</v>
       </c>
-      <c r="R11" s="72" t="str">
+      <c r="R11" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB11" s="73" t="s">
+      <c r="AB11" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="AC11" s="73" t="s">
-        <v>534</v>
+      <c r="AC11" s="59" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -5187,15 +5224,15 @@
       <c r="Q12" s="48">
         <v>23.12</v>
       </c>
-      <c r="R12" s="72" t="str">
+      <c r="R12" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB12" s="74" t="s">
+      <c r="AB12" s="60" t="s">
         <v>221</v>
       </c>
-      <c r="AC12" s="74" t="s">
-        <v>534</v>
+      <c r="AC12" s="60" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -5250,15 +5287,15 @@
       <c r="Q13" s="48">
         <v>25.88</v>
       </c>
-      <c r="R13" s="72" t="str">
+      <c r="R13" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB13" s="73" t="s">
+      <c r="AB13" s="59" t="s">
         <v>352</v>
       </c>
-      <c r="AC13" s="73" t="s">
-        <v>534</v>
+      <c r="AC13" s="59" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -5313,14 +5350,14 @@
       <c r="Q14" s="48">
         <v>26.89</v>
       </c>
-      <c r="R14" s="72" t="s">
+      <c r="R14" s="58" t="s">
         <v>476</v>
       </c>
-      <c r="AB14" s="74" t="s">
-        <v>537</v>
-      </c>
-      <c r="AC14" s="74" t="s">
-        <v>534</v>
+      <c r="AB14" s="60" t="s">
+        <v>536</v>
+      </c>
+      <c r="AC14" s="60" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -5375,14 +5412,14 @@
       <c r="Q15" s="48">
         <v>26.89</v>
       </c>
-      <c r="R15" s="72" t="s">
+      <c r="R15" s="58" t="s">
         <v>476</v>
       </c>
-      <c r="AB15" s="73" t="s">
+      <c r="AB15" s="59" t="s">
         <v>367</v>
       </c>
-      <c r="AC15" s="73" t="s">
-        <v>534</v>
+      <c r="AC15" s="59" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -5437,15 +5474,15 @@
       <c r="Q16" s="48">
         <v>29.8</v>
       </c>
-      <c r="R16" s="72" t="str">
+      <c r="R16" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB16" s="74" t="s">
+      <c r="AB16" s="60" t="s">
         <v>308</v>
       </c>
-      <c r="AC16" s="74" t="s">
-        <v>534</v>
+      <c r="AC16" s="60" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="17" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -5500,14 +5537,14 @@
       <c r="Q17" s="48">
         <v>20.53</v>
       </c>
-      <c r="R17" s="72" t="s">
-        <v>535</v>
-      </c>
-      <c r="AB17" s="73" t="s">
+      <c r="R17" s="58" t="s">
+        <v>534</v>
+      </c>
+      <c r="AB17" s="59" t="s">
         <v>223</v>
       </c>
-      <c r="AC17" s="73" t="s">
-        <v>534</v>
+      <c r="AC17" s="59" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="18" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -5562,14 +5599,14 @@
       <c r="Q18" s="48">
         <v>17.11</v>
       </c>
-      <c r="R18" s="72" t="str">
+      <c r="R18" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB18" s="74" t="s">
+      <c r="AB18" s="60" t="s">
         <v>306</v>
       </c>
-      <c r="AC18" s="74" t="s">
+      <c r="AC18" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -5625,17 +5662,17 @@
       <c r="Q19" s="48">
         <v>22.36</v>
       </c>
-      <c r="R19" s="72" t="str">
+      <c r="R19" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
       <c r="W19" s="13" t="s">
         <v>475</v>
       </c>
-      <c r="AB19" s="73" t="s">
-        <v>527</v>
-      </c>
-      <c r="AC19" s="73" t="s">
+      <c r="AB19" s="59" t="s">
+        <v>526</v>
+      </c>
+      <c r="AC19" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -5691,7 +5728,7 @@
       <c r="Q20" s="48">
         <v>22.36</v>
       </c>
-      <c r="R20" s="72" t="str">
+      <c r="R20" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -5701,10 +5738,10 @@
       <c r="X20" s="14" t="s">
         <v>479</v>
       </c>
-      <c r="AB20" s="74" t="s">
+      <c r="AB20" s="60" t="s">
         <v>358</v>
       </c>
-      <c r="AC20" s="74" t="s">
+      <c r="AC20" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -5760,8 +5797,8 @@
       <c r="Q21" s="48">
         <v>22.36</v>
       </c>
-      <c r="R21" s="72" t="s">
-        <v>535</v>
+      <c r="R21" s="58" t="s">
+        <v>534</v>
       </c>
       <c r="W21" s="21" t="s">
         <v>423</v>
@@ -5769,10 +5806,10 @@
       <c r="X21" s="14" t="s">
         <v>480</v>
       </c>
-      <c r="AB21" s="73" t="s">
+      <c r="AB21" s="59" t="s">
         <v>310</v>
       </c>
-      <c r="AC21" s="73" t="s">
+      <c r="AC21" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -5828,8 +5865,8 @@
       <c r="Q22" s="48">
         <v>22.36</v>
       </c>
-      <c r="R22" s="72" t="s">
-        <v>535</v>
+      <c r="R22" s="58" t="s">
+        <v>534</v>
       </c>
       <c r="W22" s="21" t="s">
         <v>409</v>
@@ -5837,10 +5874,10 @@
       <c r="X22" s="14" t="s">
         <v>483</v>
       </c>
-      <c r="AB22" s="74" t="s">
-        <v>538</v>
-      </c>
-      <c r="AC22" s="74" t="s">
+      <c r="AB22" s="60" t="s">
+        <v>537</v>
+      </c>
+      <c r="AC22" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -5896,7 +5933,7 @@
       <c r="Q23" s="48">
         <v>25.4</v>
       </c>
-      <c r="R23" s="72" t="str">
+      <c r="R23" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -5906,10 +5943,10 @@
       <c r="X23" s="14" t="s">
         <v>484</v>
       </c>
-      <c r="AB23" s="73" t="s">
+      <c r="AB23" s="59" t="s">
         <v>257</v>
       </c>
-      <c r="AC23" s="73" t="s">
+      <c r="AC23" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -5965,7 +6002,7 @@
       <c r="Q24" s="48">
         <v>22.36</v>
       </c>
-      <c r="R24" s="72" t="str">
+      <c r="R24" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -5975,10 +6012,10 @@
       <c r="X24" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="AB24" s="74" t="s">
+      <c r="AB24" s="60" t="s">
         <v>387</v>
       </c>
-      <c r="AC24" s="74" t="s">
+      <c r="AC24" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -6034,7 +6071,7 @@
       <c r="Q25" s="48">
         <v>22.79</v>
       </c>
-      <c r="R25" s="72" t="str">
+      <c r="R25" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -6044,10 +6081,10 @@
       <c r="X25" s="14" t="s">
         <v>487</v>
       </c>
-      <c r="AB25" s="73" t="s">
+      <c r="AB25" s="59" t="s">
         <v>360</v>
       </c>
-      <c r="AC25" s="73" t="s">
+      <c r="AC25" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -6103,7 +6140,7 @@
       <c r="Q26" s="48">
         <v>18.73</v>
       </c>
-      <c r="R26" s="72" t="str">
+      <c r="R26" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>A</v>
       </c>
@@ -6113,10 +6150,10 @@
       <c r="X26" s="14" t="s">
         <v>488</v>
       </c>
-      <c r="AB26" s="74" t="s">
+      <c r="AB26" s="60" t="s">
         <v>222</v>
       </c>
-      <c r="AC26" s="74" t="s">
+      <c r="AC26" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -6172,7 +6209,7 @@
       <c r="Q27" s="48">
         <v>18.46</v>
       </c>
-      <c r="R27" s="72" t="str">
+      <c r="R27" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>A</v>
       </c>
@@ -6182,10 +6219,10 @@
       <c r="X27" s="14" t="s">
         <v>489</v>
       </c>
-      <c r="AB27" s="73" t="s">
+      <c r="AB27" s="59" t="s">
         <v>361</v>
       </c>
-      <c r="AC27" s="73" t="s">
+      <c r="AC27" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -6241,7 +6278,7 @@
       <c r="Q28" s="48">
         <v>19.350000000000001</v>
       </c>
-      <c r="R28" s="72" t="str">
+      <c r="R28" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -6251,10 +6288,10 @@
       <c r="X28" s="14" t="s">
         <v>490</v>
       </c>
-      <c r="AB28" s="74" t="s">
+      <c r="AB28" s="60" t="s">
         <v>291</v>
       </c>
-      <c r="AC28" s="74" t="s">
+      <c r="AC28" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -6310,7 +6347,7 @@
       <c r="Q29" s="48">
         <v>20.69</v>
       </c>
-      <c r="R29" s="72" t="str">
+      <c r="R29" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
@@ -6320,10 +6357,10 @@
       <c r="X29" s="14" t="s">
         <v>493</v>
       </c>
-      <c r="AB29" s="73" t="s">
+      <c r="AB29" s="59" t="s">
         <v>321</v>
       </c>
-      <c r="AC29" s="73" t="s">
+      <c r="AC29" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -6379,7 +6416,7 @@
       <c r="Q30" s="48">
         <v>19.829999999999998</v>
       </c>
-      <c r="R30" s="72" t="str">
+      <c r="R30" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -6389,10 +6426,10 @@
       <c r="X30" s="14" t="s">
         <v>494</v>
       </c>
-      <c r="AB30" s="74" t="s">
+      <c r="AB30" s="60" t="s">
         <v>279</v>
       </c>
-      <c r="AC30" s="74" t="s">
+      <c r="AC30" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -6448,7 +6485,7 @@
       <c r="Q31" s="48">
         <v>19.55</v>
       </c>
-      <c r="R31" s="72" t="str">
+      <c r="R31" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -6458,10 +6495,10 @@
       <c r="X31" s="14" t="s">
         <v>495</v>
       </c>
-      <c r="AB31" s="73" t="s">
+      <c r="AB31" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AC31" s="73" t="s">
+      <c r="AC31" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -6517,7 +6554,7 @@
       <c r="Q32" s="48">
         <v>21.18</v>
       </c>
-      <c r="R32" s="72" t="str">
+      <c r="R32" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -6527,10 +6564,10 @@
       <c r="X32" s="14" t="s">
         <v>496</v>
       </c>
-      <c r="AB32" s="74" t="s">
+      <c r="AB32" s="60" t="s">
         <v>359</v>
       </c>
-      <c r="AC32" s="74" t="s">
+      <c r="AC32" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -6586,7 +6623,7 @@
       <c r="Q33" s="48">
         <v>23.11</v>
       </c>
-      <c r="R33" s="72" t="str">
+      <c r="R33" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -6596,10 +6633,10 @@
       <c r="X33" s="14" t="s">
         <v>497</v>
       </c>
-      <c r="AB33" s="73" t="s">
+      <c r="AB33" s="59" t="s">
         <v>245</v>
       </c>
-      <c r="AC33" s="73" t="s">
+      <c r="AC33" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -6655,7 +6692,7 @@
       <c r="Q34" s="48">
         <v>18.52</v>
       </c>
-      <c r="R34" s="72" t="str">
+      <c r="R34" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -6665,10 +6702,10 @@
       <c r="X34" s="14" t="s">
         <v>498</v>
       </c>
-      <c r="AB34" s="74" t="s">
+      <c r="AB34" s="60" t="s">
         <v>371</v>
       </c>
-      <c r="AC34" s="74" t="s">
+      <c r="AC34" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -6724,7 +6761,7 @@
       <c r="Q35" s="48">
         <v>18.36</v>
       </c>
-      <c r="R35" s="72" t="str">
+      <c r="R35" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -6734,10 +6771,10 @@
       <c r="X35" s="14" t="s">
         <v>499</v>
       </c>
-      <c r="AB35" s="73" t="s">
+      <c r="AB35" s="59" t="s">
         <v>229</v>
       </c>
-      <c r="AC35" s="73" t="s">
+      <c r="AC35" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -6793,7 +6830,7 @@
       <c r="Q36" s="48">
         <v>21.47</v>
       </c>
-      <c r="R36" s="72" t="str">
+      <c r="R36" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
@@ -6803,10 +6840,10 @@
       <c r="X36" s="14" t="s">
         <v>505</v>
       </c>
-      <c r="AB36" s="74" t="s">
+      <c r="AB36" s="60" t="s">
         <v>259</v>
       </c>
-      <c r="AC36" s="74" t="s">
+      <c r="AC36" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -6862,7 +6899,7 @@
       <c r="Q37" s="48">
         <v>19.37</v>
       </c>
-      <c r="R37" s="72" t="str">
+      <c r="R37" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -6872,10 +6909,10 @@
       <c r="X37" s="14" t="s">
         <v>506</v>
       </c>
-      <c r="AB37" s="73" t="s">
+      <c r="AB37" s="59" t="s">
         <v>301</v>
       </c>
-      <c r="AC37" s="73" t="s">
+      <c r="AC37" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -6931,7 +6968,7 @@
       <c r="Q38" s="48">
         <v>23</v>
       </c>
-      <c r="R38" s="72" t="str">
+      <c r="R38" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -6941,10 +6978,10 @@
       <c r="X38" s="14" t="s">
         <v>507</v>
       </c>
-      <c r="AB38" s="74" t="s">
+      <c r="AB38" s="60" t="s">
         <v>252</v>
       </c>
-      <c r="AC38" s="74" t="s">
+      <c r="AC38" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -7000,7 +7037,7 @@
       <c r="Q39" s="48">
         <v>19.59</v>
       </c>
-      <c r="R39" s="72" t="str">
+      <c r="R39" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -7010,10 +7047,10 @@
       <c r="X39" s="14" t="s">
         <v>508</v>
       </c>
-      <c r="AB39" s="73" t="s">
+      <c r="AB39" s="59" t="s">
         <v>375</v>
       </c>
-      <c r="AC39" s="73" t="s">
+      <c r="AC39" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -7069,7 +7106,7 @@
       <c r="Q40" s="48">
         <v>13.49</v>
       </c>
-      <c r="R40" s="72" t="str">
+      <c r="R40" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -7079,16 +7116,16 @@
       <c r="X40" s="14" t="s">
         <v>500</v>
       </c>
-      <c r="AB40" s="74" t="s">
+      <c r="AB40" s="60" t="s">
         <v>298</v>
       </c>
-      <c r="AC40" s="74" t="s">
+      <c r="AC40" s="60" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="41" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="42" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B41" s="42" t="s">
         <v>80</v>
@@ -7138,7 +7175,7 @@
       <c r="Q41" s="48">
         <v>8.39</v>
       </c>
-      <c r="R41" s="72" t="str">
+      <c r="R41" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
@@ -7148,10 +7185,10 @@
       <c r="X41" s="14" t="s">
         <v>491</v>
       </c>
-      <c r="AB41" s="73" t="s">
+      <c r="AB41" s="59" t="s">
         <v>300</v>
       </c>
-      <c r="AC41" s="73" t="s">
+      <c r="AC41" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -7207,7 +7244,7 @@
       <c r="Q42" s="48">
         <v>13.09</v>
       </c>
-      <c r="R42" s="72" t="str">
+      <c r="R42" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
@@ -7217,10 +7254,10 @@
       <c r="X42" s="14" t="s">
         <v>501</v>
       </c>
-      <c r="AB42" s="74" t="s">
+      <c r="AB42" s="60" t="s">
         <v>305</v>
       </c>
-      <c r="AC42" s="74" t="s">
+      <c r="AC42" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -7276,7 +7313,7 @@
       <c r="Q43" s="48">
         <v>21</v>
       </c>
-      <c r="R43" s="72" t="str">
+      <c r="R43" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
@@ -7286,10 +7323,10 @@
       <c r="X43" s="14" t="s">
         <v>485</v>
       </c>
-      <c r="AB43" s="73" t="s">
+      <c r="AB43" s="59" t="s">
         <v>364</v>
       </c>
-      <c r="AC43" s="73" t="s">
+      <c r="AC43" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -7345,7 +7382,7 @@
       <c r="Q44" s="48">
         <v>22.6</v>
       </c>
-      <c r="R44" s="72" t="str">
+      <c r="R44" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>A</v>
       </c>
@@ -7355,10 +7392,10 @@
       <c r="X44" s="14" t="s">
         <v>492</v>
       </c>
-      <c r="AB44" s="74" t="s">
+      <c r="AB44" s="60" t="s">
         <v>277</v>
       </c>
-      <c r="AC44" s="74" t="s">
+      <c r="AC44" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -7414,7 +7451,7 @@
       <c r="Q45" s="48">
         <v>40.479999999999997</v>
       </c>
-      <c r="R45" s="72" t="str">
+      <c r="R45" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -7424,10 +7461,10 @@
       <c r="X45" s="14" t="s">
         <v>477</v>
       </c>
-      <c r="AB45" s="73" t="s">
+      <c r="AB45" s="59" t="s">
         <v>318</v>
       </c>
-      <c r="AC45" s="73" t="s">
+      <c r="AC45" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -7483,7 +7520,7 @@
       <c r="Q46" s="48">
         <v>21.88</v>
       </c>
-      <c r="R46" s="72" t="str">
+      <c r="R46" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -7493,10 +7530,10 @@
       <c r="X46" s="14" t="s">
         <v>481</v>
       </c>
-      <c r="AB46" s="74" t="s">
+      <c r="AB46" s="60" t="s">
         <v>363</v>
       </c>
-      <c r="AC46" s="74" t="s">
+      <c r="AC46" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -7552,7 +7589,7 @@
       <c r="Q47" s="48">
         <v>40.64</v>
       </c>
-      <c r="R47" s="72" t="str">
+      <c r="R47" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -7562,10 +7599,10 @@
       <c r="X47" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="AB47" s="73" t="s">
+      <c r="AB47" s="59" t="s">
         <v>258</v>
       </c>
-      <c r="AC47" s="73" t="s">
+      <c r="AC47" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -7621,7 +7658,7 @@
       <c r="Q48" s="48">
         <v>7.28</v>
       </c>
-      <c r="R48" s="72" t="str">
+      <c r="R48" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -7631,10 +7668,10 @@
       <c r="X48" s="14" t="s">
         <v>482</v>
       </c>
-      <c r="AB48" s="74" t="s">
+      <c r="AB48" s="60" t="s">
         <v>314</v>
       </c>
-      <c r="AC48" s="74" t="s">
+      <c r="AC48" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -7690,7 +7727,7 @@
       <c r="Q49" s="48">
         <v>6.71</v>
       </c>
-      <c r="R49" s="72" t="str">
+      <c r="R49" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
@@ -7700,10 +7737,10 @@
       <c r="X49" s="14" t="s">
         <v>502</v>
       </c>
-      <c r="AB49" s="73" t="s">
+      <c r="AB49" s="59" t="s">
         <v>369</v>
       </c>
-      <c r="AC49" s="73" t="s">
+      <c r="AC49" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -7759,7 +7796,7 @@
       <c r="Q50" s="48">
         <v>21.5</v>
       </c>
-      <c r="R50" s="72" t="str">
+      <c r="R50" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -7769,10 +7806,10 @@
       <c r="X50" s="14" t="s">
         <v>503</v>
       </c>
-      <c r="AB50" s="74" t="s">
+      <c r="AB50" s="60" t="s">
         <v>365</v>
       </c>
-      <c r="AC50" s="74" t="s">
+      <c r="AC50" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -7828,7 +7865,7 @@
       <c r="Q51" s="48">
         <v>43</v>
       </c>
-      <c r="R51" s="72" t="str">
+      <c r="R51" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -7838,10 +7875,10 @@
       <c r="X51" s="14" t="s">
         <v>509</v>
       </c>
-      <c r="AB51" s="73" t="s">
+      <c r="AB51" s="59" t="s">
         <v>299</v>
       </c>
-      <c r="AC51" s="73" t="s">
+      <c r="AC51" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -7897,7 +7934,7 @@
       <c r="Q52" s="48">
         <v>16.2</v>
       </c>
-      <c r="R52" s="72" t="str">
+      <c r="R52" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -7907,10 +7944,10 @@
       <c r="X52" s="14" t="s">
         <v>504</v>
       </c>
-      <c r="AB52" s="74" t="s">
+      <c r="AB52" s="60" t="s">
         <v>224</v>
       </c>
-      <c r="AC52" s="74" t="s">
+      <c r="AC52" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -7966,7 +8003,7 @@
       <c r="Q53" s="48">
         <v>17.260000000000002</v>
       </c>
-      <c r="R53" s="72" t="str">
+      <c r="R53" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -7976,10 +8013,10 @@
       <c r="X53" s="14" t="s">
         <v>486</v>
       </c>
-      <c r="AB53" s="73" t="s">
+      <c r="AB53" s="59" t="s">
         <v>362</v>
       </c>
-      <c r="AC53" s="73" t="s">
+      <c r="AC53" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -8035,7 +8072,7 @@
       <c r="Q54" s="48">
         <v>25.29</v>
       </c>
-      <c r="R54" s="72" t="str">
+      <c r="R54" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -8045,10 +8082,10 @@
       <c r="X54" s="14" t="s">
         <v>510</v>
       </c>
-      <c r="AB54" s="74" t="s">
+      <c r="AB54" s="60" t="s">
         <v>386</v>
       </c>
-      <c r="AC54" s="74" t="s">
+      <c r="AC54" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -8104,14 +8141,14 @@
       <c r="Q55" s="48">
         <v>19.45</v>
       </c>
-      <c r="R55" s="72" t="str">
+      <c r="R55" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB55" s="73" t="s">
+      <c r="AB55" s="59" t="s">
         <v>271</v>
       </c>
-      <c r="AC55" s="73" t="s">
+      <c r="AC55" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -8167,13 +8204,13 @@
       <c r="Q56" s="48">
         <v>19.37</v>
       </c>
-      <c r="R56" s="72" t="s">
-        <v>535</v>
-      </c>
-      <c r="AB56" s="74" t="s">
+      <c r="R56" s="58" t="s">
+        <v>534</v>
+      </c>
+      <c r="AB56" s="60" t="s">
         <v>341</v>
       </c>
-      <c r="AC56" s="74" t="s">
+      <c r="AC56" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -8229,13 +8266,13 @@
       <c r="Q57" s="48">
         <v>16.2</v>
       </c>
-      <c r="R57" s="72" t="s">
-        <v>535</v>
-      </c>
-      <c r="AB57" s="73" t="s">
+      <c r="R57" s="58" t="s">
+        <v>534</v>
+      </c>
+      <c r="AB57" s="59" t="s">
         <v>289</v>
       </c>
-      <c r="AC57" s="73" t="s">
+      <c r="AC57" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -8291,13 +8328,13 @@
       <c r="Q58" s="48">
         <v>30.68</v>
       </c>
-      <c r="R58" s="72" t="s">
-        <v>535</v>
-      </c>
-      <c r="AB58" s="74" t="s">
+      <c r="R58" s="58" t="s">
+        <v>534</v>
+      </c>
+      <c r="AB58" s="60" t="s">
         <v>372</v>
       </c>
-      <c r="AC58" s="74" t="s">
+      <c r="AC58" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -8353,13 +8390,13 @@
       <c r="Q59" s="48">
         <v>33.520000000000003</v>
       </c>
-      <c r="R59" s="72" t="s">
-        <v>535</v>
-      </c>
-      <c r="AB59" s="73" t="s">
+      <c r="R59" s="58" t="s">
+        <v>534</v>
+      </c>
+      <c r="AB59" s="59" t="s">
         <v>265</v>
       </c>
-      <c r="AC59" s="73" t="s">
+      <c r="AC59" s="59" t="s">
         <v>476</v>
       </c>
     </row>
@@ -8415,14 +8452,14 @@
       <c r="Q60" s="48">
         <v>32.26</v>
       </c>
-      <c r="R60" s="72" t="str">
+      <c r="R60" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB60" s="74" t="s">
+      <c r="AB60" s="60" t="s">
         <v>322</v>
       </c>
-      <c r="AC60" s="74" t="s">
+      <c r="AC60" s="60" t="s">
         <v>476</v>
       </c>
     </row>
@@ -8478,15 +8515,15 @@
       <c r="Q61" s="48">
         <v>33.57</v>
       </c>
-      <c r="R61" s="72" t="str">
+      <c r="R61" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB61" s="73" t="s">
-        <v>521</v>
-      </c>
-      <c r="AC61" s="73" t="s">
-        <v>535</v>
+      <c r="AB61" s="59" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC61" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="62" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -8541,14 +8578,14 @@
       <c r="Q62" s="48">
         <v>34.03</v>
       </c>
-      <c r="R62" s="72" t="s">
+      <c r="R62" s="58" t="s">
         <v>476</v>
       </c>
-      <c r="AB62" s="74" t="s">
-        <v>539</v>
-      </c>
-      <c r="AC62" s="74" t="s">
-        <v>535</v>
+      <c r="AB62" s="60" t="s">
+        <v>538</v>
+      </c>
+      <c r="AC62" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="63" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -8603,15 +8640,15 @@
       <c r="Q63" s="48">
         <v>16.850000000000001</v>
       </c>
-      <c r="R63" s="72" t="str">
+      <c r="R63" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB63" s="73" t="s">
+      <c r="AB63" s="59" t="s">
         <v>250</v>
       </c>
-      <c r="AC63" s="73" t="s">
-        <v>535</v>
+      <c r="AC63" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="64" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -8666,15 +8703,15 @@
       <c r="Q64" s="48">
         <v>22.94</v>
       </c>
-      <c r="R64" s="72" t="str">
+      <c r="R64" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB64" s="74" t="s">
+      <c r="AB64" s="60" t="s">
         <v>328</v>
       </c>
-      <c r="AC64" s="74" t="s">
-        <v>535</v>
+      <c r="AC64" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="65" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -8729,15 +8766,15 @@
       <c r="Q65" s="48">
         <v>16.87</v>
       </c>
-      <c r="R65" s="72" t="str">
+      <c r="R65" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB65" s="73" t="s">
+      <c r="AB65" s="59" t="s">
         <v>368</v>
       </c>
-      <c r="AC65" s="73" t="s">
-        <v>535</v>
+      <c r="AC65" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="66" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -8792,15 +8829,15 @@
       <c r="Q66" s="48">
         <v>16.309999999999999</v>
       </c>
-      <c r="R66" s="72" t="str">
+      <c r="R66" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB66" s="74" t="s">
+      <c r="AB66" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="AC66" s="74" t="s">
-        <v>535</v>
+      <c r="AC66" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="67" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -8855,15 +8892,15 @@
       <c r="Q67" s="48">
         <v>27.08</v>
       </c>
-      <c r="R67" s="72" t="str">
+      <c r="R67" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB67" s="73" t="s">
+      <c r="AB67" s="59" t="s">
         <v>373</v>
       </c>
-      <c r="AC67" s="73" t="s">
-        <v>535</v>
+      <c r="AC67" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="68" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -8918,14 +8955,14 @@
       <c r="Q68" s="48">
         <v>21.55</v>
       </c>
-      <c r="R68" s="72" t="s">
+      <c r="R68" s="58" t="s">
         <v>476</v>
       </c>
-      <c r="AB68" s="74" t="s">
+      <c r="AB68" s="60" t="s">
         <v>391</v>
       </c>
-      <c r="AC68" s="74" t="s">
-        <v>535</v>
+      <c r="AC68" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="69" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -8980,14 +9017,14 @@
       <c r="Q69" s="48">
         <v>16.850000000000001</v>
       </c>
-      <c r="R69" s="72" t="s">
-        <v>535</v>
-      </c>
-      <c r="AB69" s="73" t="s">
+      <c r="R69" s="58" t="s">
+        <v>534</v>
+      </c>
+      <c r="AB69" s="59" t="s">
         <v>333</v>
       </c>
-      <c r="AC69" s="73" t="s">
-        <v>535</v>
+      <c r="AC69" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="70" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9042,15 +9079,15 @@
       <c r="Q70" s="48">
         <v>17.73</v>
       </c>
-      <c r="R70" s="72" t="str">
+      <c r="R70" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB70" s="74" t="s">
+      <c r="AB70" s="60" t="s">
         <v>295</v>
       </c>
-      <c r="AC70" s="74" t="s">
-        <v>535</v>
+      <c r="AC70" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="71" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9105,15 +9142,15 @@
       <c r="Q71" s="48">
         <v>33.74</v>
       </c>
-      <c r="R71" s="72" t="str">
+      <c r="R71" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB71" s="73" t="s">
+      <c r="AB71" s="59" t="s">
         <v>235</v>
       </c>
-      <c r="AC71" s="73" t="s">
-        <v>535</v>
+      <c r="AC71" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="72" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9168,15 +9205,15 @@
       <c r="Q72" s="48">
         <v>37.49</v>
       </c>
-      <c r="R72" s="72" t="str">
+      <c r="R72" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB72" s="74" t="s">
+      <c r="AB72" s="60" t="s">
         <v>377</v>
       </c>
-      <c r="AC72" s="74" t="s">
-        <v>535</v>
+      <c r="AC72" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="73" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9231,15 +9268,15 @@
       <c r="Q73" s="48">
         <v>29.58</v>
       </c>
-      <c r="R73" s="72" t="str">
+      <c r="R73" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB73" s="73" t="s">
+      <c r="AB73" s="59" t="s">
         <v>311</v>
       </c>
-      <c r="AC73" s="73" t="s">
-        <v>535</v>
+      <c r="AC73" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="74" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9294,15 +9331,15 @@
       <c r="Q74" s="48">
         <v>13.78</v>
       </c>
-      <c r="R74" s="72" t="str">
+      <c r="R74" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB74" s="74" t="s">
+      <c r="AB74" s="60" t="s">
         <v>282</v>
       </c>
-      <c r="AC74" s="74" t="s">
-        <v>535</v>
+      <c r="AC74" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="75" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9357,15 +9394,15 @@
       <c r="Q75" s="48">
         <v>21</v>
       </c>
-      <c r="R75" s="72" t="str">
+      <c r="R75" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB75" s="73" t="s">
+      <c r="AB75" s="59" t="s">
         <v>236</v>
       </c>
-      <c r="AC75" s="73" t="s">
-        <v>535</v>
+      <c r="AC75" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="76" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9420,15 +9457,15 @@
       <c r="Q76" s="48">
         <v>15.51</v>
       </c>
-      <c r="R76" s="72" t="str">
+      <c r="R76" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB76" s="74" t="s">
+      <c r="AB76" s="60" t="s">
         <v>339</v>
       </c>
-      <c r="AC76" s="74" t="s">
-        <v>535</v>
+      <c r="AC76" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="77" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9483,15 +9520,15 @@
       <c r="Q77" s="48">
         <v>14.71</v>
       </c>
-      <c r="R77" s="72" t="str">
+      <c r="R77" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB77" s="73" t="s">
+      <c r="AB77" s="59" t="s">
         <v>313</v>
       </c>
-      <c r="AC77" s="73" t="s">
-        <v>535</v>
+      <c r="AC77" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="78" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9546,15 +9583,15 @@
       <c r="Q78" s="48">
         <v>8.39</v>
       </c>
-      <c r="R78" s="72" t="str">
+      <c r="R78" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB78" s="74" t="s">
+      <c r="AB78" s="60" t="s">
         <v>366</v>
       </c>
-      <c r="AC78" s="74" t="s">
-        <v>535</v>
+      <c r="AC78" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="79" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9609,15 +9646,15 @@
       <c r="Q79" s="48">
         <v>32.46</v>
       </c>
-      <c r="R79" s="72" t="str">
+      <c r="R79" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB79" s="73" t="s">
+      <c r="AB79" s="59" t="s">
         <v>244</v>
       </c>
-      <c r="AC79" s="73" t="s">
-        <v>535</v>
+      <c r="AC79" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="80" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9672,15 +9709,15 @@
       <c r="Q80" s="48">
         <v>37.74</v>
       </c>
-      <c r="R80" s="72" t="str">
+      <c r="R80" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB80" s="74" t="s">
+      <c r="AB80" s="60" t="s">
         <v>326</v>
       </c>
-      <c r="AC80" s="74" t="s">
-        <v>535</v>
+      <c r="AC80" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="81" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9735,15 +9772,15 @@
       <c r="Q81" s="48">
         <v>8.9700000000000006</v>
       </c>
-      <c r="R81" s="72" t="str">
+      <c r="R81" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>A</v>
       </c>
-      <c r="AB81" s="73" t="s">
+      <c r="AB81" s="59" t="s">
         <v>297</v>
       </c>
-      <c r="AC81" s="73" t="s">
-        <v>535</v>
+      <c r="AC81" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="82" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9798,15 +9835,15 @@
       <c r="Q82" s="48">
         <v>21.88</v>
       </c>
-      <c r="R82" s="72" t="str">
+      <c r="R82" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB82" s="74" t="s">
+      <c r="AB82" s="60" t="s">
         <v>357</v>
       </c>
-      <c r="AC82" s="74" t="s">
-        <v>535</v>
+      <c r="AC82" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="83" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9861,15 +9898,15 @@
       <c r="Q83" s="48">
         <v>40.64</v>
       </c>
-      <c r="R83" s="72" t="str">
+      <c r="R83" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB83" s="73" t="s">
+      <c r="AB83" s="59" t="s">
         <v>266</v>
       </c>
-      <c r="AC83" s="73" t="s">
-        <v>535</v>
+      <c r="AC83" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="84" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9924,15 +9961,15 @@
       <c r="Q84" s="48">
         <v>32.21</v>
       </c>
-      <c r="R84" s="72" t="str">
+      <c r="R84" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB84" s="74" t="s">
+      <c r="AB84" s="60" t="s">
         <v>293</v>
       </c>
-      <c r="AC84" s="74" t="s">
-        <v>535</v>
+      <c r="AC84" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="85" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -9987,15 +10024,15 @@
       <c r="Q85" s="48">
         <v>19.8</v>
       </c>
-      <c r="R85" s="72" t="str">
+      <c r="R85" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB85" s="73" t="s">
+      <c r="AB85" s="59" t="s">
         <v>329</v>
       </c>
-      <c r="AC85" s="73" t="s">
-        <v>535</v>
+      <c r="AC85" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="86" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10050,15 +10087,15 @@
       <c r="Q86" s="48">
         <v>35.36</v>
       </c>
-      <c r="R86" s="72" t="str">
+      <c r="R86" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB86" s="74" t="s">
+      <c r="AB86" s="60" t="s">
         <v>348</v>
       </c>
-      <c r="AC86" s="74" t="s">
-        <v>535</v>
+      <c r="AC86" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="87" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10113,15 +10150,15 @@
       <c r="Q87" s="48">
         <v>19.54</v>
       </c>
-      <c r="R87" s="72" t="str">
+      <c r="R87" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>-</v>
       </c>
-      <c r="AB87" s="73" t="s">
-        <v>525</v>
-      </c>
-      <c r="AC87" s="73" t="s">
-        <v>535</v>
+      <c r="AB87" s="59" t="s">
+        <v>524</v>
+      </c>
+      <c r="AC87" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="88" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10176,15 +10213,15 @@
       <c r="Q88" s="48">
         <v>19.54</v>
       </c>
-      <c r="R88" s="72" t="str">
+      <c r="R88" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB88" s="74" t="s">
+      <c r="AB88" s="60" t="s">
         <v>290</v>
       </c>
-      <c r="AC88" s="74" t="s">
-        <v>535</v>
+      <c r="AC88" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="89" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10239,15 +10276,15 @@
       <c r="Q89" s="48">
         <v>19.54</v>
       </c>
-      <c r="R89" s="72" t="str">
+      <c r="R89" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>-</v>
       </c>
-      <c r="AB89" s="73" t="s">
+      <c r="AB89" s="59" t="s">
         <v>312</v>
       </c>
-      <c r="AC89" s="73" t="s">
-        <v>535</v>
+      <c r="AC89" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="90" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10302,15 +10339,15 @@
       <c r="Q90" s="48">
         <v>30.94</v>
       </c>
-      <c r="R90" s="72" t="str">
+      <c r="R90" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB90" s="74" t="s">
+      <c r="AB90" s="60" t="s">
         <v>351</v>
       </c>
-      <c r="AC90" s="74" t="s">
-        <v>535</v>
+      <c r="AC90" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="91" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10365,15 +10402,15 @@
       <c r="Q91" s="48">
         <v>28.47</v>
       </c>
-      <c r="R91" s="72" t="str">
+      <c r="R91" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB91" s="73" t="s">
+      <c r="AB91" s="59" t="s">
         <v>309</v>
       </c>
-      <c r="AC91" s="73" t="s">
-        <v>535</v>
+      <c r="AC91" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="92" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10428,15 +10465,15 @@
       <c r="Q92" s="48">
         <v>28.47</v>
       </c>
-      <c r="R92" s="72" t="str">
+      <c r="R92" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB92" s="74" t="s">
+      <c r="AB92" s="60" t="s">
         <v>276</v>
       </c>
-      <c r="AC92" s="74" t="s">
-        <v>535</v>
+      <c r="AC92" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="93" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10491,15 +10528,15 @@
       <c r="Q93" s="48">
         <v>30.94</v>
       </c>
-      <c r="R93" s="72" t="str">
+      <c r="R93" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB93" s="73" t="s">
+      <c r="AB93" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="AC93" s="73" t="s">
-        <v>535</v>
+      <c r="AC93" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="94" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10554,15 +10591,15 @@
       <c r="Q94" s="48">
         <v>22.97</v>
       </c>
-      <c r="R94" s="72" t="str">
+      <c r="R94" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>A</v>
       </c>
-      <c r="AB94" s="74" t="s">
+      <c r="AB94" s="60" t="s">
         <v>336</v>
       </c>
-      <c r="AC94" s="74" t="s">
-        <v>535</v>
+      <c r="AC94" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="95" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10617,15 +10654,15 @@
       <c r="Q95" s="48">
         <v>16.88</v>
       </c>
-      <c r="R95" s="72" t="str">
+      <c r="R95" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB95" s="73" t="s">
+      <c r="AB95" s="59" t="s">
         <v>327</v>
       </c>
-      <c r="AC95" s="73" t="s">
-        <v>535</v>
+      <c r="AC95" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="96" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10678,15 +10715,15 @@
       <c r="Q96" s="48">
         <v>32.17</v>
       </c>
-      <c r="R96" s="72" t="str">
+      <c r="R96" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB96" s="74" t="s">
+      <c r="AB96" s="60" t="s">
         <v>344</v>
       </c>
-      <c r="AC96" s="74" t="s">
-        <v>535</v>
+      <c r="AC96" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="97" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10739,15 +10776,15 @@
       <c r="Q97" s="48">
         <v>23.43</v>
       </c>
-      <c r="R97" s="72" t="str">
+      <c r="R97" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB97" s="73" t="s">
-        <v>540</v>
-      </c>
-      <c r="AC97" s="73" t="s">
-        <v>535</v>
+      <c r="AB97" s="59" t="s">
+        <v>539</v>
+      </c>
+      <c r="AC97" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="98" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10802,15 +10839,15 @@
       <c r="Q98" s="48">
         <v>15.16</v>
       </c>
-      <c r="R98" s="72" t="str">
+      <c r="R98" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB98" s="74" t="s">
+      <c r="AB98" s="60" t="s">
         <v>286</v>
       </c>
-      <c r="AC98" s="74" t="s">
-        <v>535</v>
+      <c r="AC98" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="99" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10865,15 +10902,15 @@
       <c r="Q99" s="48">
         <v>17.22</v>
       </c>
-      <c r="R99" s="72" t="str">
+      <c r="R99" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB99" s="73" t="s">
+      <c r="AB99" s="59" t="s">
         <v>378</v>
       </c>
-      <c r="AC99" s="73" t="s">
-        <v>535</v>
+      <c r="AC99" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="100" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10928,15 +10965,15 @@
       <c r="Q100" s="48">
         <v>13.65</v>
       </c>
-      <c r="R100" s="72" t="str">
+      <c r="R100" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB100" s="74" t="s">
+      <c r="AB100" s="60" t="s">
         <v>261</v>
       </c>
-      <c r="AC100" s="74" t="s">
-        <v>535</v>
+      <c r="AC100" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="101" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -10991,14 +11028,14 @@
       <c r="Q101" s="48">
         <v>13.65</v>
       </c>
-      <c r="R101" s="72" t="s">
-        <v>535</v>
-      </c>
-      <c r="AB101" s="73" t="s">
+      <c r="R101" s="58" t="s">
+        <v>534</v>
+      </c>
+      <c r="AB101" s="59" t="s">
         <v>513</v>
       </c>
-      <c r="AC101" s="73" t="s">
-        <v>535</v>
+      <c r="AC101" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="102" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11051,14 +11088,14 @@
       <c r="Q102" s="48">
         <v>19.68</v>
       </c>
-      <c r="R102" s="72" t="s">
-        <v>535</v>
-      </c>
-      <c r="AB102" s="74" t="s">
-        <v>541</v>
-      </c>
-      <c r="AC102" s="74" t="s">
-        <v>535</v>
+      <c r="R102" s="58" t="s">
+        <v>534</v>
+      </c>
+      <c r="AB102" s="60" t="s">
+        <v>540</v>
+      </c>
+      <c r="AC102" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="103" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11111,15 +11148,15 @@
       <c r="Q103" s="48">
         <v>30.68</v>
       </c>
-      <c r="R103" s="72" t="str">
+      <c r="R103" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB103" s="73" t="s">
+      <c r="AB103" s="59" t="s">
         <v>246</v>
       </c>
-      <c r="AC103" s="73" t="s">
-        <v>535</v>
+      <c r="AC103" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="104" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11172,15 +11209,15 @@
       <c r="Q104" s="48">
         <v>18.72</v>
       </c>
-      <c r="R104" s="72" t="str">
+      <c r="R104" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB104" s="74" t="s">
+      <c r="AB104" s="60" t="s">
         <v>343</v>
       </c>
-      <c r="AC104" s="74" t="s">
-        <v>535</v>
+      <c r="AC104" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="105" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11235,15 +11272,15 @@
       <c r="Q105" s="48">
         <v>37.619999999999997</v>
       </c>
-      <c r="R105" s="72" t="str">
+      <c r="R105" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB105" s="73" t="s">
+      <c r="AB105" s="59" t="s">
         <v>269</v>
       </c>
-      <c r="AC105" s="73" t="s">
-        <v>535</v>
+      <c r="AC105" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="106" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11298,15 +11335,15 @@
       <c r="Q106" s="48">
         <v>37.619999999999997</v>
       </c>
-      <c r="R106" s="72" t="str">
+      <c r="R106" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB106" s="74" t="s">
+      <c r="AB106" s="60" t="s">
         <v>355</v>
       </c>
-      <c r="AC106" s="74" t="s">
-        <v>535</v>
+      <c r="AC106" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="107" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11361,15 +11398,15 @@
       <c r="Q107" s="48">
         <v>30.98</v>
       </c>
-      <c r="R107" s="72" t="str">
+      <c r="R107" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB107" s="73" t="s">
+      <c r="AB107" s="59" t="s">
         <v>354</v>
       </c>
-      <c r="AC107" s="73" t="s">
-        <v>535</v>
+      <c r="AC107" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="108" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11424,15 +11461,15 @@
       <c r="Q108" s="48">
         <v>28.81</v>
       </c>
-      <c r="R108" s="72" t="str">
+      <c r="R108" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB108" s="74" t="s">
+      <c r="AB108" s="60" t="s">
         <v>512</v>
       </c>
-      <c r="AC108" s="74" t="s">
-        <v>535</v>
+      <c r="AC108" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="109" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11487,15 +11524,15 @@
       <c r="Q109" s="48">
         <v>15.81</v>
       </c>
-      <c r="R109" s="72" t="str">
+      <c r="R109" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB109" s="73" t="s">
+      <c r="AB109" s="59" t="s">
         <v>287</v>
       </c>
-      <c r="AC109" s="73" t="s">
-        <v>535</v>
+      <c r="AC109" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="110" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11550,15 +11587,15 @@
       <c r="Q110" s="48">
         <v>37.94</v>
       </c>
-      <c r="R110" s="72" t="str">
+      <c r="R110" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB110" s="74" t="s">
+      <c r="AB110" s="60" t="s">
         <v>337</v>
       </c>
-      <c r="AC110" s="74" t="s">
-        <v>535</v>
+      <c r="AC110" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="111" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11613,15 +11650,15 @@
       <c r="Q111" s="48">
         <v>8.8000000000000007</v>
       </c>
-      <c r="R111" s="72" t="str">
+      <c r="R111" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>A</v>
       </c>
-      <c r="AB111" s="73" t="s">
+      <c r="AB111" s="59" t="s">
         <v>268</v>
       </c>
-      <c r="AC111" s="73" t="s">
-        <v>535</v>
+      <c r="AC111" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="112" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11676,15 +11713,15 @@
       <c r="Q112" s="48">
         <v>9.34</v>
       </c>
-      <c r="R112" s="72" t="str">
+      <c r="R112" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB112" s="74" t="s">
+      <c r="AB112" s="60" t="s">
         <v>241</v>
       </c>
-      <c r="AC112" s="74" t="s">
-        <v>535</v>
+      <c r="AC112" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="113" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11739,15 +11776,15 @@
       <c r="Q113" s="48">
         <v>8.98</v>
       </c>
-      <c r="R113" s="72" t="str">
+      <c r="R113" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB113" s="73" t="s">
+      <c r="AB113" s="59" t="s">
         <v>240</v>
       </c>
-      <c r="AC113" s="73" t="s">
-        <v>535</v>
+      <c r="AC113" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="114" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11802,15 +11839,15 @@
       <c r="Q114" s="48">
         <v>37.94</v>
       </c>
-      <c r="R114" s="72" t="str">
+      <c r="R114" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB114" s="74" t="s">
+      <c r="AB114" s="60" t="s">
         <v>228</v>
       </c>
-      <c r="AC114" s="74" t="s">
-        <v>535</v>
+      <c r="AC114" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="115" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11865,15 +11902,15 @@
       <c r="Q115" s="48">
         <v>8.9700000000000006</v>
       </c>
-      <c r="R115" s="72" t="str">
+      <c r="R115" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB115" s="73" t="s">
+      <c r="AB115" s="59" t="s">
         <v>331</v>
       </c>
-      <c r="AC115" s="73" t="s">
-        <v>535</v>
+      <c r="AC115" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="116" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11928,15 +11965,15 @@
       <c r="Q116" s="48">
         <v>10.06</v>
       </c>
-      <c r="R116" s="72" t="str">
+      <c r="R116" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB116" s="74" t="s">
+      <c r="AB116" s="60" t="s">
         <v>248</v>
       </c>
-      <c r="AC116" s="74" t="s">
-        <v>535</v>
+      <c r="AC116" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="117" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -11991,15 +12028,15 @@
       <c r="Q117" s="48">
         <v>8.08</v>
       </c>
-      <c r="R117" s="72" t="str">
+      <c r="R117" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB117" s="73" t="s">
+      <c r="AB117" s="59" t="s">
         <v>249</v>
       </c>
-      <c r="AC117" s="73" t="s">
-        <v>535</v>
+      <c r="AC117" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="118" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12054,15 +12091,15 @@
       <c r="Q118" s="48">
         <v>37.94</v>
       </c>
-      <c r="R118" s="72" t="str">
+      <c r="R118" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB118" s="74" t="s">
+      <c r="AB118" s="60" t="s">
         <v>255</v>
       </c>
-      <c r="AC118" s="74" t="s">
-        <v>535</v>
+      <c r="AC118" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="119" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12117,15 +12154,15 @@
       <c r="Q119" s="48">
         <v>16.93</v>
       </c>
-      <c r="R119" s="72" t="str">
+      <c r="R119" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB119" s="73" t="s">
+      <c r="AB119" s="59" t="s">
         <v>370</v>
       </c>
-      <c r="AC119" s="73" t="s">
-        <v>535</v>
+      <c r="AC119" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="120" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12180,15 +12217,15 @@
       <c r="Q120" s="48">
         <v>37.94</v>
       </c>
-      <c r="R120" s="72" t="str">
+      <c r="R120" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB120" s="74" t="s">
-        <v>542</v>
-      </c>
-      <c r="AC120" s="74" t="s">
-        <v>535</v>
+      <c r="AB120" s="60" t="s">
+        <v>541</v>
+      </c>
+      <c r="AC120" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="121" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12243,15 +12280,15 @@
       <c r="Q121" s="48">
         <v>17.78</v>
       </c>
-      <c r="R121" s="72" t="str">
+      <c r="R121" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB121" s="73" t="s">
+      <c r="AB121" s="59" t="s">
         <v>283</v>
       </c>
-      <c r="AC121" s="73" t="s">
-        <v>535</v>
+      <c r="AC121" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="122" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12306,15 +12343,15 @@
       <c r="Q122" s="48">
         <v>17.78</v>
       </c>
-      <c r="R122" s="72" t="str">
+      <c r="R122" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB122" s="74" t="s">
+      <c r="AB122" s="60" t="s">
         <v>288</v>
       </c>
-      <c r="AC122" s="74" t="s">
-        <v>535</v>
+      <c r="AC122" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="123" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12369,15 +12406,15 @@
       <c r="Q123" s="48">
         <v>16.559999999999999</v>
       </c>
-      <c r="R123" s="72" t="str">
+      <c r="R123" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB123" s="73" t="s">
+      <c r="AB123" s="59" t="s">
         <v>294</v>
       </c>
-      <c r="AC123" s="73" t="s">
-        <v>535</v>
+      <c r="AC123" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="124" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12432,15 +12469,15 @@
       <c r="Q124" s="48">
         <v>17.78</v>
       </c>
-      <c r="R124" s="72" t="str">
+      <c r="R124" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB124" s="74" t="s">
+      <c r="AB124" s="60" t="s">
         <v>280</v>
       </c>
-      <c r="AC124" s="74" t="s">
-        <v>535</v>
+      <c r="AC124" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="125" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12495,15 +12532,15 @@
       <c r="Q125" s="48">
         <v>13.68</v>
       </c>
-      <c r="R125" s="72" t="str">
+      <c r="R125" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB125" s="73" t="s">
+      <c r="AB125" s="59" t="s">
         <v>349</v>
       </c>
-      <c r="AC125" s="73" t="s">
-        <v>535</v>
+      <c r="AC125" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="126" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12558,15 +12595,15 @@
       <c r="Q126" s="48">
         <v>17.28</v>
       </c>
-      <c r="R126" s="72" t="str">
+      <c r="R126" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB126" s="74" t="s">
+      <c r="AB126" s="60" t="s">
         <v>379</v>
       </c>
-      <c r="AC126" s="74" t="s">
-        <v>535</v>
+      <c r="AC126" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="127" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12621,15 +12658,15 @@
       <c r="Q127" s="48">
         <v>17.28</v>
       </c>
-      <c r="R127" s="72" t="str">
+      <c r="R127" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB127" s="73" t="s">
+      <c r="AB127" s="59" t="s">
         <v>234</v>
       </c>
-      <c r="AC127" s="73" t="s">
-        <v>535</v>
+      <c r="AC127" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="128" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12684,15 +12721,15 @@
       <c r="Q128" s="48">
         <v>17.28</v>
       </c>
-      <c r="R128" s="72" t="str">
+      <c r="R128" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB128" s="74" t="s">
+      <c r="AB128" s="60" t="s">
         <v>385</v>
       </c>
-      <c r="AC128" s="74" t="s">
-        <v>535</v>
+      <c r="AC128" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="129" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12747,15 +12784,15 @@
       <c r="Q129" s="48">
         <v>13.68</v>
       </c>
-      <c r="R129" s="72" t="str">
+      <c r="R129" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB129" s="73" t="s">
+      <c r="AB129" s="59" t="s">
         <v>317</v>
       </c>
-      <c r="AC129" s="73" t="s">
-        <v>535</v>
+      <c r="AC129" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="130" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12810,15 +12847,15 @@
       <c r="Q130" s="48">
         <v>16.489999999999998</v>
       </c>
-      <c r="R130" s="72" t="str">
+      <c r="R130" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB130" s="74" t="s">
+      <c r="AB130" s="60" t="s">
         <v>239</v>
       </c>
-      <c r="AC130" s="74" t="s">
-        <v>535</v>
+      <c r="AC130" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="131" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12873,15 +12910,15 @@
       <c r="Q131" s="48">
         <v>14.57</v>
       </c>
-      <c r="R131" s="72" t="str">
+      <c r="R131" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB131" s="73" t="s">
+      <c r="AB131" s="59" t="s">
         <v>247</v>
       </c>
-      <c r="AC131" s="73" t="s">
-        <v>535</v>
+      <c r="AC131" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="132" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12936,15 +12973,15 @@
       <c r="Q132" s="48">
         <v>16.489999999999998</v>
       </c>
-      <c r="R132" s="72" t="str">
+      <c r="R132" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB132" s="74" t="s">
+      <c r="AB132" s="60" t="s">
         <v>253</v>
       </c>
-      <c r="AC132" s="74" t="s">
-        <v>535</v>
+      <c r="AC132" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="133" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -12999,15 +13036,15 @@
       <c r="Q133" s="48">
         <v>16.489999999999998</v>
       </c>
-      <c r="R133" s="72" t="str">
+      <c r="R133" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB133" s="73" t="s">
+      <c r="AB133" s="59" t="s">
         <v>226</v>
       </c>
-      <c r="AC133" s="73" t="s">
-        <v>535</v>
+      <c r="AC133" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="134" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -13062,15 +13099,15 @@
       <c r="Q134" s="48">
         <v>16.489999999999998</v>
       </c>
-      <c r="R134" s="72" t="str">
+      <c r="R134" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB134" s="74" t="s">
+      <c r="AB134" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="AC134" s="74" t="s">
-        <v>535</v>
+      <c r="AC134" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="135" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -13125,15 +13162,15 @@
       <c r="Q135" s="48">
         <v>13.81</v>
       </c>
-      <c r="R135" s="72" t="str">
+      <c r="R135" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB135" s="73" t="s">
+      <c r="AB135" s="59" t="s">
         <v>225</v>
       </c>
-      <c r="AC135" s="73" t="s">
-        <v>535</v>
+      <c r="AC135" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="136" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -13188,15 +13225,15 @@
       <c r="Q136" s="48">
         <v>16.489999999999998</v>
       </c>
-      <c r="R136" s="72" t="str">
+      <c r="R136" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB136" s="74" t="s">
+      <c r="AB136" s="60" t="s">
         <v>232</v>
       </c>
-      <c r="AC136" s="74" t="s">
-        <v>535</v>
+      <c r="AC136" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="137" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -13251,15 +13288,15 @@
       <c r="Q137" s="48">
         <v>13.24</v>
       </c>
-      <c r="R137" s="72" t="str">
+      <c r="R137" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB137" s="73" t="s">
+      <c r="AB137" s="59" t="s">
         <v>254</v>
       </c>
-      <c r="AC137" s="73" t="s">
-        <v>535</v>
+      <c r="AC137" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="138" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -13314,15 +13351,15 @@
       <c r="Q138" s="48">
         <v>11.34</v>
       </c>
-      <c r="R138" s="72" t="str">
+      <c r="R138" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>A</v>
       </c>
-      <c r="AB138" s="74" t="s">
+      <c r="AB138" s="60" t="s">
         <v>340</v>
       </c>
-      <c r="AC138" s="74" t="s">
-        <v>535</v>
+      <c r="AC138" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="139" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -13377,15 +13414,15 @@
       <c r="Q139" s="48">
         <v>16.489999999999998</v>
       </c>
-      <c r="R139" s="72" t="str">
+      <c r="R139" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB139" s="73" t="s">
+      <c r="AB139" s="59" t="s">
         <v>330</v>
       </c>
-      <c r="AC139" s="73" t="s">
-        <v>535</v>
+      <c r="AC139" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="140" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -13440,15 +13477,15 @@
       <c r="Q140" s="48">
         <v>16.489999999999998</v>
       </c>
-      <c r="R140" s="72" t="str">
+      <c r="R140" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB140" s="74" t="s">
+      <c r="AB140" s="60" t="s">
         <v>281</v>
       </c>
-      <c r="AC140" s="74" t="s">
-        <v>535</v>
+      <c r="AC140" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="141" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -13503,15 +13540,15 @@
       <c r="Q141" s="48">
         <v>14.86</v>
       </c>
-      <c r="R141" s="72" t="str">
+      <c r="R141" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB141" s="73" t="s">
+      <c r="AB141" s="59" t="s">
         <v>323</v>
       </c>
-      <c r="AC141" s="73" t="s">
-        <v>535</v>
+      <c r="AC141" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="142" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -13566,15 +13603,15 @@
       <c r="Q142" s="48">
         <v>16.489999999999998</v>
       </c>
-      <c r="R142" s="72" t="str">
+      <c r="R142" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB142" s="74" t="s">
-        <v>543</v>
-      </c>
-      <c r="AC142" s="74" t="s">
-        <v>535</v>
+      <c r="AB142" s="60" t="s">
+        <v>542</v>
+      </c>
+      <c r="AC142" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="143" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -13629,15 +13666,15 @@
       <c r="Q143" s="48">
         <v>13.24</v>
       </c>
-      <c r="R143" s="72" t="str">
+      <c r="R143" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB143" s="73" t="s">
-        <v>544</v>
-      </c>
-      <c r="AC143" s="73" t="s">
-        <v>535</v>
+      <c r="AB143" s="59" t="s">
+        <v>543</v>
+      </c>
+      <c r="AC143" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="144" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -13692,15 +13729,15 @@
       <c r="Q144" s="48">
         <v>32.32</v>
       </c>
-      <c r="R144" s="72" t="str">
+      <c r="R144" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB144" s="74" t="s">
+      <c r="AB144" s="60" t="s">
         <v>356</v>
       </c>
-      <c r="AC144" s="74" t="s">
-        <v>535</v>
+      <c r="AC144" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="145" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -13755,15 +13792,15 @@
       <c r="Q145" s="48">
         <v>30.59</v>
       </c>
-      <c r="R145" s="72" t="str">
+      <c r="R145" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB145" s="73" t="s">
+      <c r="AB145" s="59" t="s">
         <v>381</v>
       </c>
-      <c r="AC145" s="73" t="s">
-        <v>535</v>
+      <c r="AC145" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="146" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -13818,15 +13855,15 @@
       <c r="Q146" s="48">
         <v>32.35</v>
       </c>
-      <c r="R146" s="72" t="str">
+      <c r="R146" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB146" s="74" t="s">
+      <c r="AB146" s="60" t="s">
         <v>383</v>
       </c>
-      <c r="AC146" s="74" t="s">
-        <v>535</v>
+      <c r="AC146" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="147" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -13881,15 +13918,15 @@
       <c r="Q147" s="48">
         <v>31.03</v>
       </c>
-      <c r="R147" s="72" t="str">
+      <c r="R147" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB147" s="73" t="s">
+      <c r="AB147" s="59" t="s">
         <v>350</v>
       </c>
-      <c r="AC147" s="73" t="s">
-        <v>535</v>
+      <c r="AC147" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="148" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -13944,15 +13981,15 @@
       <c r="Q148" s="48">
         <v>32.81</v>
       </c>
-      <c r="R148" s="72" t="str">
+      <c r="R148" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB148" s="74" t="s">
+      <c r="AB148" s="60" t="s">
         <v>346</v>
       </c>
-      <c r="AC148" s="74" t="s">
-        <v>535</v>
+      <c r="AC148" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="149" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14007,15 +14044,15 @@
       <c r="Q149" s="48">
         <v>30.59</v>
       </c>
-      <c r="R149" s="72" t="str">
+      <c r="R149" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB149" s="73" t="s">
+      <c r="AB149" s="59" t="s">
         <v>342</v>
       </c>
-      <c r="AC149" s="73" t="s">
-        <v>535</v>
+      <c r="AC149" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="150" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14070,15 +14107,15 @@
       <c r="Q150" s="48">
         <v>32.35</v>
       </c>
-      <c r="R150" s="72" t="str">
+      <c r="R150" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB150" s="74" t="s">
+      <c r="AB150" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="AC150" s="74" t="s">
-        <v>535</v>
+      <c r="AC150" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="151" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14133,15 +14170,15 @@
       <c r="Q151" s="48">
         <v>26.32</v>
       </c>
-      <c r="R151" s="72" t="str">
+      <c r="R151" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB151" s="73" t="s">
+      <c r="AB151" s="59" t="s">
         <v>264</v>
       </c>
-      <c r="AC151" s="73" t="s">
-        <v>535</v>
+      <c r="AC151" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="152" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14196,15 +14233,15 @@
       <c r="Q152" s="48">
         <v>23.46</v>
       </c>
-      <c r="R152" s="72" t="str">
+      <c r="R152" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB152" s="74" t="s">
+      <c r="AB152" s="60" t="s">
         <v>262</v>
       </c>
-      <c r="AC152" s="74" t="s">
-        <v>535</v>
+      <c r="AC152" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="153" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14259,15 +14296,15 @@
       <c r="Q153" s="48">
         <v>24.75</v>
       </c>
-      <c r="R153" s="72" t="str">
+      <c r="R153" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>A</v>
       </c>
-      <c r="AB153" s="73" t="s">
+      <c r="AB153" s="59" t="s">
         <v>332</v>
       </c>
-      <c r="AC153" s="73" t="s">
-        <v>535</v>
+      <c r="AC153" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="154" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14322,15 +14359,15 @@
       <c r="Q154" s="48">
         <v>23.46</v>
       </c>
-      <c r="R154" s="72" t="str">
+      <c r="R154" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB154" s="74" t="s">
+      <c r="AB154" s="60" t="s">
         <v>251</v>
       </c>
-      <c r="AC154" s="74" t="s">
-        <v>535</v>
+      <c r="AC154" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="155" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14385,15 +14422,15 @@
       <c r="Q155" s="48">
         <v>26.32</v>
       </c>
-      <c r="R155" s="72" t="str">
+      <c r="R155" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB155" s="73" t="s">
+      <c r="AB155" s="59" t="s">
         <v>334</v>
       </c>
-      <c r="AC155" s="73" t="s">
-        <v>535</v>
+      <c r="AC155" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="156" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14448,15 +14485,15 @@
       <c r="Q156" s="48">
         <v>23.46</v>
       </c>
-      <c r="R156" s="72" t="str">
+      <c r="R156" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB156" s="74" t="s">
-        <v>545</v>
-      </c>
-      <c r="AC156" s="74" t="s">
-        <v>535</v>
+      <c r="AB156" s="60" t="s">
+        <v>544</v>
+      </c>
+      <c r="AC156" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="157" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14511,15 +14548,15 @@
       <c r="Q157" s="48">
         <v>33.42</v>
       </c>
-      <c r="R157" s="72" t="str">
+      <c r="R157" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB157" s="73" t="s">
+      <c r="AB157" s="59" t="s">
         <v>263</v>
       </c>
-      <c r="AC157" s="73" t="s">
-        <v>535</v>
+      <c r="AC157" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="158" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14574,15 +14611,15 @@
       <c r="Q158" s="48">
         <v>16.989999999999998</v>
       </c>
-      <c r="R158" s="72" t="str">
+      <c r="R158" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB158" s="74" t="s">
+      <c r="AB158" s="60" t="s">
         <v>319</v>
       </c>
-      <c r="AC158" s="74" t="s">
-        <v>535</v>
+      <c r="AC158" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="159" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14637,15 +14674,15 @@
       <c r="Q159" s="48">
         <v>40.909999999999997</v>
       </c>
-      <c r="R159" s="72" t="str">
+      <c r="R159" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB159" s="73" t="s">
+      <c r="AB159" s="59" t="s">
         <v>320</v>
       </c>
-      <c r="AC159" s="73" t="s">
-        <v>535</v>
+      <c r="AC159" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="160" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14700,15 +14737,15 @@
       <c r="Q160" s="48">
         <v>9.85</v>
       </c>
-      <c r="R160" s="72" t="str">
+      <c r="R160" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB160" s="74" t="s">
-        <v>546</v>
-      </c>
-      <c r="AC160" s="74" t="s">
-        <v>535</v>
+      <c r="AB160" s="60" t="s">
+        <v>545</v>
+      </c>
+      <c r="AC160" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="161" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14763,15 +14800,15 @@
       <c r="Q161" s="48">
         <v>15.68</v>
       </c>
-      <c r="R161" s="72" t="str">
+      <c r="R161" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB161" s="73" t="s">
+      <c r="AB161" s="59" t="s">
         <v>227</v>
       </c>
-      <c r="AC161" s="73" t="s">
-        <v>535</v>
+      <c r="AC161" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="162" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14826,15 +14863,15 @@
       <c r="Q162" s="48">
         <v>28.96</v>
       </c>
-      <c r="R162" s="72" t="str">
+      <c r="R162" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>A</v>
       </c>
-      <c r="AB162" s="74" t="s">
+      <c r="AB162" s="60" t="s">
         <v>392</v>
       </c>
-      <c r="AC162" s="74" t="s">
-        <v>535</v>
+      <c r="AC162" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="163" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14889,15 +14926,15 @@
       <c r="Q163" s="48">
         <v>25.39</v>
       </c>
-      <c r="R163" s="72" t="str">
+      <c r="R163" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB163" s="73" t="s">
+      <c r="AB163" s="59" t="s">
         <v>394</v>
       </c>
-      <c r="AC163" s="73" t="s">
-        <v>535</v>
+      <c r="AC163" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="164" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -14952,15 +14989,15 @@
       <c r="Q164" s="48">
         <v>15.67</v>
       </c>
-      <c r="R164" s="72" t="str">
+      <c r="R164" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB164" s="74" t="s">
+      <c r="AB164" s="60" t="s">
         <v>345</v>
       </c>
-      <c r="AC164" s="74" t="s">
-        <v>535</v>
+      <c r="AC164" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="165" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -15015,15 +15052,15 @@
       <c r="Q165" s="48">
         <v>17.02</v>
       </c>
-      <c r="R165" s="72" t="str">
+      <c r="R165" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB165" s="73" t="s">
+      <c r="AB165" s="59" t="s">
         <v>256</v>
       </c>
-      <c r="AC165" s="73" t="s">
-        <v>535</v>
+      <c r="AC165" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="166" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -15078,14 +15115,14 @@
       <c r="Q166" s="48">
         <v>14.29</v>
       </c>
-      <c r="R166" s="72" t="s">
-        <v>535</v>
-      </c>
-      <c r="AB166" s="74" t="s">
-        <v>547</v>
-      </c>
-      <c r="AC166" s="74" t="s">
-        <v>535</v>
+      <c r="R166" s="58" t="s">
+        <v>534</v>
+      </c>
+      <c r="AB166" s="60" t="s">
+        <v>546</v>
+      </c>
+      <c r="AC166" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="167" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -15140,15 +15177,15 @@
       <c r="Q167" s="48">
         <v>14.86</v>
       </c>
-      <c r="R167" s="72" t="str">
+      <c r="R167" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB167" s="73" t="s">
+      <c r="AB167" s="59" t="s">
         <v>335</v>
       </c>
-      <c r="AC167" s="73" t="s">
-        <v>535</v>
+      <c r="AC167" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="168" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -15203,14 +15240,14 @@
       <c r="Q168" s="48">
         <v>14.57</v>
       </c>
-      <c r="R168" s="72" t="s">
-        <v>535</v>
-      </c>
-      <c r="AB168" s="74" t="s">
+      <c r="R168" s="58" t="s">
+        <v>534</v>
+      </c>
+      <c r="AB168" s="60" t="s">
         <v>393</v>
       </c>
-      <c r="AC168" s="74" t="s">
-        <v>535</v>
+      <c r="AC168" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="169" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -15265,15 +15302,15 @@
       <c r="Q169" s="48">
         <v>16.559999999999999</v>
       </c>
-      <c r="R169" s="72" t="str">
+      <c r="R169" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB169" s="73" t="s">
-        <v>548</v>
-      </c>
-      <c r="AC169" s="73" t="s">
-        <v>535</v>
+      <c r="AB169" s="59" t="s">
+        <v>547</v>
+      </c>
+      <c r="AC169" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="170" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -15328,15 +15365,15 @@
       <c r="Q170" s="48">
         <v>28.8</v>
       </c>
-      <c r="R170" s="72" t="str">
+      <c r="R170" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB170" s="74" t="s">
-        <v>549</v>
-      </c>
-      <c r="AC170" s="74" t="s">
-        <v>535</v>
+      <c r="AB170" s="60" t="s">
+        <v>548</v>
+      </c>
+      <c r="AC170" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="171" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -15391,15 +15428,15 @@
       <c r="Q171" s="48">
         <v>43.05</v>
       </c>
-      <c r="R171" s="72" t="str">
+      <c r="R171" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB171" s="73" t="s">
+      <c r="AB171" s="59" t="s">
         <v>347</v>
       </c>
-      <c r="AC171" s="73" t="s">
-        <v>535</v>
+      <c r="AC171" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="172" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -15454,15 +15491,15 @@
       <c r="Q172" s="48">
         <v>32.17</v>
       </c>
-      <c r="R172" s="72" t="str">
+      <c r="R172" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB172" s="74" t="s">
+      <c r="AB172" s="60" t="s">
         <v>353</v>
       </c>
-      <c r="AC172" s="74" t="s">
-        <v>535</v>
+      <c r="AC172" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="173" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -15517,15 +15554,15 @@
       <c r="Q173" s="48">
         <v>32.17</v>
       </c>
-      <c r="R173" s="72" t="str">
+      <c r="R173" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>B</v>
       </c>
-      <c r="AB173" s="73" t="s">
+      <c r="AB173" s="59" t="s">
         <v>338</v>
       </c>
-      <c r="AC173" s="73" t="s">
-        <v>535</v>
+      <c r="AC173" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="174" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -15580,14 +15617,14 @@
       <c r="Q174" s="48">
         <v>8.8000000000000007</v>
       </c>
-      <c r="R174" s="72" t="s">
+      <c r="R174" s="58" t="s">
+        <v>533</v>
+      </c>
+      <c r="AB174" s="60" t="s">
+        <v>292</v>
+      </c>
+      <c r="AC174" s="60" t="s">
         <v>534</v>
-      </c>
-      <c r="AB174" s="74" t="s">
-        <v>292</v>
-      </c>
-      <c r="AC174" s="74" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="175" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -15642,14 +15679,14 @@
       <c r="Q175" s="48">
         <v>8.8000000000000007</v>
       </c>
-      <c r="R175" s="72" t="s">
+      <c r="R175" s="58" t="s">
+        <v>533</v>
+      </c>
+      <c r="AB175" s="59" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC175" s="59" t="s">
         <v>534</v>
-      </c>
-      <c r="AB175" s="73" t="s">
-        <v>303</v>
-      </c>
-      <c r="AC175" s="73" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="176" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -15704,14 +15741,14 @@
       <c r="Q176" s="48">
         <v>19.5</v>
       </c>
-      <c r="R176" s="72" t="s">
-        <v>535</v>
-      </c>
-      <c r="AB176" s="74" t="s">
-        <v>550</v>
-      </c>
-      <c r="AC176" s="74" t="s">
-        <v>535</v>
+      <c r="R176" s="58" t="s">
+        <v>534</v>
+      </c>
+      <c r="AB176" s="60" t="s">
+        <v>549</v>
+      </c>
+      <c r="AC176" s="60" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="177" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -15766,15 +15803,15 @@
       <c r="Q177" s="48">
         <v>21.55</v>
       </c>
-      <c r="R177" s="72" t="str">
+      <c r="R177" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB177" s="73" t="s">
+      <c r="AB177" s="59" t="s">
         <v>384</v>
       </c>
-      <c r="AC177" s="73" t="s">
-        <v>535</v>
+      <c r="AC177" s="59" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="178" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -15829,14 +15866,14 @@
       <c r="Q178" s="48">
         <v>19.02</v>
       </c>
-      <c r="R178" s="72" t="str">
+      <c r="R178" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB178" s="74" t="s">
-        <v>551</v>
-      </c>
-      <c r="AC178" s="74" t="s">
+      <c r="AB178" s="60" t="s">
+        <v>550</v>
+      </c>
+      <c r="AC178" s="60" t="s">
         <v>35</v>
       </c>
     </row>
@@ -15892,14 +15929,14 @@
       <c r="Q179" s="48">
         <v>19.12</v>
       </c>
-      <c r="R179" s="72" t="str">
+      <c r="R179" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB179" s="73" t="s">
-        <v>552</v>
-      </c>
-      <c r="AC179" s="73" t="s">
+      <c r="AB179" s="59" t="s">
+        <v>551</v>
+      </c>
+      <c r="AC179" s="59" t="s">
         <v>35</v>
       </c>
     </row>
@@ -15955,14 +15992,14 @@
       <c r="Q180" s="48">
         <v>19.12</v>
       </c>
-      <c r="R180" s="72" t="str">
+      <c r="R180" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
-      <c r="AB180" s="74" t="s">
-        <v>553</v>
-      </c>
-      <c r="AC180" s="74" t="s">
+      <c r="AB180" s="60" t="s">
+        <v>552</v>
+      </c>
+      <c r="AC180" s="60" t="s">
         <v>35</v>
       </c>
     </row>
@@ -16018,13 +16055,13 @@
       <c r="Q181" s="48">
         <v>8.8000000000000007</v>
       </c>
-      <c r="R181" s="72" t="s">
-        <v>534</v>
-      </c>
-      <c r="AB181" s="73" t="s">
+      <c r="R181" s="58" t="s">
+        <v>533</v>
+      </c>
+      <c r="AB181" s="59" t="s">
         <v>304</v>
       </c>
-      <c r="AC181" s="73" t="s">
+      <c r="AC181" s="59" t="s">
         <v>35</v>
       </c>
     </row>
@@ -16080,13 +16117,13 @@
       <c r="Q182" s="48">
         <v>9.34</v>
       </c>
-      <c r="R182" s="72" t="s">
-        <v>534</v>
-      </c>
-      <c r="AB182" s="74" t="s">
+      <c r="R182" s="58" t="s">
+        <v>533</v>
+      </c>
+      <c r="AB182" s="60" t="s">
         <v>302</v>
       </c>
-      <c r="AC182" s="74" t="s">
+      <c r="AC182" s="60" t="s">
         <v>35</v>
       </c>
     </row>
@@ -16142,8 +16179,8 @@
       <c r="Q183" s="48">
         <v>9.34</v>
       </c>
-      <c r="R183" s="72" t="s">
-        <v>534</v>
+      <c r="R183" s="58" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="184" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -16198,8 +16235,8 @@
       <c r="Q184" s="48">
         <v>8.8000000000000007</v>
       </c>
-      <c r="R184" s="72" t="s">
-        <v>534</v>
+      <c r="R184" s="58" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="185" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -16254,8 +16291,8 @@
       <c r="Q185" s="48">
         <v>8.8000000000000007</v>
       </c>
-      <c r="R185" s="72" t="s">
-        <v>534</v>
+      <c r="R185" s="58" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="186" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -16310,8 +16347,8 @@
       <c r="Q186" s="48">
         <v>30.4</v>
       </c>
-      <c r="R186" s="72" t="s">
-        <v>535</v>
+      <c r="R186" s="58" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="187" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -16319,7 +16356,7 @@
         <v>514</v>
       </c>
       <c r="B187" s="42" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C187" s="42">
         <v>4</v>
@@ -16366,16 +16403,16 @@
       <c r="Q187" s="48">
         <v>16.87</v>
       </c>
-      <c r="R187" s="72" t="s">
-        <v>535</v>
+      <c r="R187" s="58" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="188" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A188" s="42" t="s">
-        <v>515</v>
+        <v>557</v>
       </c>
       <c r="B188" s="42" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C188" s="42">
         <v>4</v>
@@ -16422,8 +16459,8 @@
       <c r="Q188" s="48">
         <v>16.87</v>
       </c>
-      <c r="R188" s="72" t="s">
-        <v>535</v>
+      <c r="R188" s="58" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="189" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
@@ -16431,7 +16468,7 @@
         <v>512</v>
       </c>
       <c r="B189" s="42" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C189" s="42">
         <v>4</v>
@@ -16478,7 +16515,7 @@
       <c r="Q189" s="48">
         <v>39.58</v>
       </c>
-      <c r="R189" s="72" t="str">
+      <c r="R189" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -16488,7 +16525,7 @@
         <v>513</v>
       </c>
       <c r="B190" s="42" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C190" s="42">
         <v>24</v>
@@ -16535,17 +16572,17 @@
       <c r="Q190" s="48">
         <v>12.05</v>
       </c>
-      <c r="R190" s="72" t="str">
+      <c r="R190" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
     </row>
     <row r="191" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A191" s="42" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B191" s="42" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C191" s="42">
         <v>4</v>
@@ -16592,17 +16629,17 @@
       <c r="Q191" s="48">
         <v>16.78</v>
       </c>
-      <c r="R191" s="72" t="str">
+      <c r="R191" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
     </row>
     <row r="192" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A192" s="42" t="s">
+        <v>524</v>
+      </c>
+      <c r="B192" s="42" t="s">
         <v>525</v>
-      </c>
-      <c r="B192" s="42" t="s">
-        <v>526</v>
       </c>
       <c r="C192" s="42">
         <v>30</v>
@@ -16649,7 +16686,7 @@
       <c r="Q192" s="48">
         <v>19.87</v>
       </c>
-      <c r="R192" s="72" t="str">
+      <c r="R192" s="58" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[ref_id]],$AB$5:$AB$182,$AC$5:$AC$182)</f>
         <v>C</v>
       </c>
@@ -16661,13 +16698,13 @@
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="AC5:AC182">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>IF(OR(AC5="Z",AC5="C"),1,0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>IF(OR(AC5="A",AC5="X"),1,0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>IF(OR(AC5="B",AC5="Y"),1,0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16705,109 +16742,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="59"/>
-      <c r="R1" s="59"/>
-      <c r="S1" s="59"/>
-      <c r="T1" s="59"/>
-      <c r="U1" s="59"/>
-      <c r="V1" s="59"/>
-      <c r="W1" s="59"/>
-      <c r="X1" s="59"/>
-      <c r="Y1" s="59"/>
-      <c r="Z1" s="59"/>
-      <c r="AA1" s="59"/>
-      <c r="AB1" s="59"/>
-      <c r="AC1" s="59"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="62" t="s">
         <v>400</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="63"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="63"/>
+      <c r="Y2" s="63"/>
+      <c r="Z2" s="63"/>
+      <c r="AA2" s="63"/>
+      <c r="AB2" s="63"/>
+      <c r="AC2" s="63"/>
     </row>
     <row r="3" spans="1:38" ht="32" x14ac:dyDescent="0.7">
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="75" t="s">
         <v>511</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="71"/>
-      <c r="P3" s="71"/>
-      <c r="Q3" s="71"/>
-      <c r="R3" s="71"/>
-      <c r="S3" s="71"/>
-      <c r="T3" s="71"/>
-      <c r="U3" s="71"/>
-      <c r="V3" s="71"/>
-      <c r="W3" s="71"/>
-      <c r="X3" s="71"/>
-      <c r="Y3" s="71"/>
-      <c r="Z3" s="71"/>
-      <c r="AA3" s="71"/>
-      <c r="AB3" s="71"/>
-      <c r="AC3" s="71"/>
-      <c r="AD3" s="71"/>
-      <c r="AE3" s="71"/>
-      <c r="AF3" s="71"/>
-      <c r="AG3" s="71"/>
-      <c r="AH3" s="71"/>
-      <c r="AI3" s="71"/>
-      <c r="AJ3" s="71"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="75"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="W3" s="75"/>
+      <c r="X3" s="75"/>
+      <c r="Y3" s="75"/>
+      <c r="Z3" s="75"/>
+      <c r="AA3" s="75"/>
+      <c r="AB3" s="75"/>
+      <c r="AC3" s="75"/>
+      <c r="AD3" s="75"/>
+      <c r="AE3" s="75"/>
+      <c r="AF3" s="75"/>
+      <c r="AG3" s="75"/>
+      <c r="AH3" s="75"/>
+      <c r="AI3" s="75"/>
+      <c r="AJ3" s="75"/>
     </row>
     <row r="4" spans="1:38" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
@@ -20799,33 +20836,35 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="B1:J85"/>
+  <dimension ref="B1:M96"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14" style="6" customWidth="1"/>
     <col min="3" max="3" width="18" style="14" customWidth="1"/>
     <col min="4" max="4" width="24.26953125" style="38" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" customWidth="1"/>
-    <col min="7" max="7" width="25.08984375" customWidth="1"/>
-    <col min="8" max="8" width="29.90625" customWidth="1"/>
-    <col min="11" max="11" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.26953125" customWidth="1"/>
+    <col min="7" max="8" width="8.7265625" style="14"/>
+    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="25.08984375" customWidth="1"/>
+    <col min="11" max="11" width="29.90625" customWidth="1"/>
+    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B1" s="60" t="s">
+    <row r="1" spans="2:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B1" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-    </row>
-    <row r="2" spans="2:8" ht="35" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="58" t="s">
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+    </row>
+    <row r="2" spans="2:11" ht="35" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="62" t="s">
         <v>404</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-    </row>
-    <row r="4" spans="2:8" ht="45" x14ac:dyDescent="0.35">
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+    </row>
+    <row r="4" spans="2:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B4" s="35" t="s">
         <v>28</v>
       </c>
@@ -20835,17 +20874,29 @@
       <c r="D4" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="E4" s="36" t="s">
+        <v>553</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>555</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>554</v>
+      </c>
+      <c r="H4" s="61" t="s">
+        <v>556</v>
+      </c>
+      <c r="I4" s="54" t="s">
+        <v>527</v>
+      </c>
+      <c r="J4" s="54" t="s">
         <v>528</v>
       </c>
-      <c r="G4" s="54" t="s">
+      <c r="K4" s="54" t="s">
         <v>529</v>
       </c>
-      <c r="H4" s="54" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="2:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B5" s="34" t="s">
         <v>224</v>
       </c>
@@ -20855,17 +20906,35 @@
       <c r="D5" s="37">
         <v>46203</v>
       </c>
-      <c r="F5" s="55" t="s">
-        <v>531</v>
-      </c>
-      <c r="G5" s="56">
-        <v>165.92526540126542</v>
-      </c>
-      <c r="H5" s="57">
+      <c r="E5" s="6">
+        <f>_xlfn.XLOOKUP(B5,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>180</v>
+      </c>
+      <c r="F5" s="6">
+        <f>(G5*C5)/E5</f>
+        <v>1.8666666666666667</v>
+      </c>
+      <c r="G5" s="14">
+        <f>_xlfn.XLOOKUP(B5,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H5" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B5,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+      <c r="I5" s="55" t="s">
+        <v>530</v>
+      </c>
+      <c r="J5" s="56">
+        <f>SUMIFS(F5:F96,H5:H96,"Sim")</f>
+        <v>190.70987757847459</v>
+      </c>
+      <c r="K5" s="57">
+        <f>18*7.5</f>
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B6" s="34" t="s">
         <v>229</v>
       </c>
@@ -20875,17 +20944,35 @@
       <c r="D6" s="37">
         <v>46203</v>
       </c>
-      <c r="F6" s="55" t="s">
-        <v>532</v>
-      </c>
-      <c r="G6" s="56">
-        <v>241.03174325966435</v>
-      </c>
-      <c r="H6" s="57">
+      <c r="E6" s="6">
+        <f>_xlfn.XLOOKUP(B6,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>220</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" ref="F6:F69" si="0">(G6*C6)/E6</f>
+        <v>1.5272727272727273</v>
+      </c>
+      <c r="G6" s="14">
+        <f>_xlfn.XLOOKUP(B6,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H6" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B6,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+      <c r="I6" s="55" t="s">
+        <v>531</v>
+      </c>
+      <c r="J6" s="56">
+        <f>SUMIFS(F5:F96,H5:H96,"Não")</f>
+        <v>235.73642747019068</v>
+      </c>
+      <c r="K6" s="57">
+        <f>18*7.5</f>
         <v>135</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B7" s="34" t="s">
         <v>372</v>
       </c>
@@ -20895,10 +20982,26 @@
       <c r="D7" s="37">
         <v>46177</v>
       </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E7" s="6">
+        <f>_xlfn.XLOOKUP(B7,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>1824</v>
+      </c>
+      <c r="F7" s="6">
+        <f t="shared" si="0"/>
+        <v>0.63157894736842102</v>
+      </c>
+      <c r="G7" s="14">
+        <f>_xlfn.XLOOKUP(B7,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H7" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B7,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B8" s="34" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C8" s="34">
         <v>140</v>
@@ -20906,8 +21009,24 @@
       <c r="D8" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E8" s="6">
+        <f>_xlfn.XLOOKUP(B8,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>126</v>
+      </c>
+      <c r="F8" s="6">
+        <f t="shared" si="0"/>
+        <v>4.4444444444444446</v>
+      </c>
+      <c r="G8" s="14">
+        <f>_xlfn.XLOOKUP(B8,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H8" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B8,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B9" s="34" t="s">
         <v>234</v>
       </c>
@@ -20917,8 +21036,24 @@
       <c r="D9" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E9" s="6">
+        <f>_xlfn.XLOOKUP(B9,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>672</v>
+      </c>
+      <c r="F9" s="6">
+        <f t="shared" si="0"/>
+        <v>6.25</v>
+      </c>
+      <c r="G9" s="14">
+        <f>_xlfn.XLOOKUP(B9,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>30</v>
+      </c>
+      <c r="H9" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B9,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B10" s="34" t="s">
         <v>259</v>
       </c>
@@ -20928,8 +21063,24 @@
       <c r="D10" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E10" s="6">
+        <f>_xlfn.XLOOKUP(B10,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>220</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" si="0"/>
+        <v>2.7272727272727271</v>
+      </c>
+      <c r="G10" s="14">
+        <f>_xlfn.XLOOKUP(B10,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H10" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B10,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B11" s="34" t="s">
         <v>374</v>
       </c>
@@ -20939,8 +21090,24 @@
       <c r="D11" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E11" s="6">
+        <f>_xlfn.XLOOKUP(B11,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>240</v>
+      </c>
+      <c r="F11" s="6">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="G11" s="14">
+        <f>_xlfn.XLOOKUP(B11,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>30</v>
+      </c>
+      <c r="H11" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B11,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B12" s="34" t="s">
         <v>269</v>
       </c>
@@ -20950,8 +21117,24 @@
       <c r="D12" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E12" s="6">
+        <f>_xlfn.XLOOKUP(B12,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>250</v>
+      </c>
+      <c r="F12" s="6">
+        <f t="shared" si="0"/>
+        <v>1.92</v>
+      </c>
+      <c r="G12" s="14">
+        <f>_xlfn.XLOOKUP(B12,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H12" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B12,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B13" s="34" t="s">
         <v>306</v>
       </c>
@@ -20961,8 +21144,24 @@
       <c r="D13" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E13" s="6">
+        <f>_xlfn.XLOOKUP(B13,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>125</v>
+      </c>
+      <c r="F13" s="6">
+        <f t="shared" si="0"/>
+        <v>4.6079999999999997</v>
+      </c>
+      <c r="G13" s="14">
+        <f>_xlfn.XLOOKUP(B13,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>3</v>
+      </c>
+      <c r="H13" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B13,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B14" s="34" t="s">
         <v>318</v>
       </c>
@@ -20972,8 +21171,24 @@
       <c r="D14" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E14" s="6">
+        <f>_xlfn.XLOOKUP(B14,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>240</v>
+      </c>
+      <c r="F14" s="6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G14" s="14">
+        <f>_xlfn.XLOOKUP(B14,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H14" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B14,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B15" s="34" t="s">
         <v>322</v>
       </c>
@@ -20983,8 +21198,24 @@
       <c r="D15" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E15" s="6">
+        <f>_xlfn.XLOOKUP(B15,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>220</v>
+      </c>
+      <c r="F15" s="6">
+        <f t="shared" si="0"/>
+        <v>1.9636363636363636</v>
+      </c>
+      <c r="G15" s="14">
+        <f>_xlfn.XLOOKUP(B15,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>3</v>
+      </c>
+      <c r="H15" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B15,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B16" s="34" t="s">
         <v>337</v>
       </c>
@@ -20994,8 +21225,24 @@
       <c r="D16" s="37">
         <v>46177</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E16" s="6">
+        <f>_xlfn.XLOOKUP(B16,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>2268</v>
+      </c>
+      <c r="F16" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G16" s="14">
+        <f>_xlfn.XLOOKUP(B16,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>21</v>
+      </c>
+      <c r="H16" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B16,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B17" s="34" t="s">
         <v>378</v>
       </c>
@@ -21005,8 +21252,24 @@
       <c r="D17" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E17" s="6">
+        <f>_xlfn.XLOOKUP(B17,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>2268</v>
+      </c>
+      <c r="F17" s="6">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G17" s="14">
+        <f>_xlfn.XLOOKUP(B17,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>21</v>
+      </c>
+      <c r="H17" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B17,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B18" s="34" t="s">
         <v>512</v>
       </c>
@@ -21016,8 +21279,24 @@
       <c r="D18" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E18" s="6">
+        <f>_xlfn.XLOOKUP(B18,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>130</v>
+      </c>
+      <c r="F18" s="6">
+        <f t="shared" si="0"/>
+        <v>2.5846153846153848</v>
+      </c>
+      <c r="G18" s="14">
+        <f>_xlfn.XLOOKUP(B18,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H18" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B18,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B19" s="34" t="s">
         <v>239</v>
       </c>
@@ -21027,8 +21306,24 @@
       <c r="D19" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E19" s="6">
+        <f>_xlfn.XLOOKUP(B19,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>240</v>
+      </c>
+      <c r="F19" s="6">
+        <f t="shared" si="0"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="G19" s="14">
+        <f>_xlfn.XLOOKUP(B19,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>48</v>
+      </c>
+      <c r="H19" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B19,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B20" s="34" t="s">
         <v>242</v>
       </c>
@@ -21038,8 +21333,24 @@
       <c r="D20" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E20" s="6">
+        <f>_xlfn.XLOOKUP(B20,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>3456</v>
+      </c>
+      <c r="F20" s="6">
+        <f t="shared" si="0"/>
+        <v>19.53125</v>
+      </c>
+      <c r="G20" s="14">
+        <f>_xlfn.XLOOKUP(B20,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>90</v>
+      </c>
+      <c r="H20" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B20,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B21" s="34" t="s">
         <v>243</v>
       </c>
@@ -21049,8 +21360,24 @@
       <c r="D21" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E21" s="6">
+        <f>_xlfn.XLOOKUP(B21,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>3456</v>
+      </c>
+      <c r="F21" s="6">
+        <f t="shared" si="0"/>
+        <v>5.208333333333333</v>
+      </c>
+      <c r="G21" s="14">
+        <f>_xlfn.XLOOKUP(B21,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>90</v>
+      </c>
+      <c r="H21" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B21,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B22" s="34" t="s">
         <v>244</v>
       </c>
@@ -21060,8 +21387,24 @@
       <c r="D22" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E22" s="6">
+        <f>_xlfn.XLOOKUP(B22,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>3456</v>
+      </c>
+      <c r="F22" s="6">
+        <f t="shared" si="0"/>
+        <v>2.6041666666666665</v>
+      </c>
+      <c r="G22" s="14">
+        <f>_xlfn.XLOOKUP(B22,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>90</v>
+      </c>
+      <c r="H22" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B22,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B23" s="34" t="s">
         <v>245</v>
       </c>
@@ -21071,8 +21414,24 @@
       <c r="D23" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E23" s="6">
+        <f>_xlfn.XLOOKUP(B23,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>3456</v>
+      </c>
+      <c r="F23" s="6">
+        <f t="shared" si="0"/>
+        <v>6.875</v>
+      </c>
+      <c r="G23" s="14">
+        <f>_xlfn.XLOOKUP(B23,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>90</v>
+      </c>
+      <c r="H23" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B23,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B24" s="34" t="s">
         <v>246</v>
       </c>
@@ -21082,8 +21441,24 @@
       <c r="D24" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E24" s="6">
+        <f>_xlfn.XLOOKUP(B24,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>2304</v>
+      </c>
+      <c r="F24" s="6">
+        <f t="shared" si="0"/>
+        <v>1.1875</v>
+      </c>
+      <c r="G24" s="14">
+        <f>_xlfn.XLOOKUP(B24,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>57</v>
+      </c>
+      <c r="H24" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B24,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B25" s="34" t="s">
         <v>252</v>
       </c>
@@ -21093,8 +21468,24 @@
       <c r="D25" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E25" s="6">
+        <f>_xlfn.XLOOKUP(B25,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>2304</v>
+      </c>
+      <c r="F25" s="6">
+        <f t="shared" si="0"/>
+        <v>1.1875</v>
+      </c>
+      <c r="G25" s="14">
+        <f>_xlfn.XLOOKUP(B25,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>57</v>
+      </c>
+      <c r="H25" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B25,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B26" s="34" t="s">
         <v>249</v>
       </c>
@@ -21104,8 +21495,24 @@
       <c r="D26" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E26" s="6">
+        <f>_xlfn.XLOOKUP(B26,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>2304</v>
+      </c>
+      <c r="F26" s="6">
+        <f t="shared" si="0"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="G26" s="14">
+        <f>_xlfn.XLOOKUP(B26,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>32</v>
+      </c>
+      <c r="H26" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B26,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B27" s="34" t="s">
         <v>250</v>
       </c>
@@ -21115,8 +21522,24 @@
       <c r="D27" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E27" s="6">
+        <f>_xlfn.XLOOKUP(B27,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>3456</v>
+      </c>
+      <c r="F27" s="6">
+        <f t="shared" si="0"/>
+        <v>5.208333333333333</v>
+      </c>
+      <c r="G27" s="14">
+        <f>_xlfn.XLOOKUP(B27,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>90</v>
+      </c>
+      <c r="H27" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B27,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B28" s="34" t="s">
         <v>251</v>
       </c>
@@ -21126,10 +21549,26 @@
       <c r="D28" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E28" s="6">
+        <f>_xlfn.XLOOKUP(B28,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>2304</v>
+      </c>
+      <c r="F28" s="6">
+        <f t="shared" si="0"/>
+        <v>2.375</v>
+      </c>
+      <c r="G28" s="14">
+        <f>_xlfn.XLOOKUP(B28,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>57</v>
+      </c>
+      <c r="H28" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B28,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B29" s="34" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C29" s="34">
         <v>192</v>
@@ -21137,8 +21576,24 @@
       <c r="D29" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E29" s="6">
+        <f>_xlfn.XLOOKUP(B29,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>126</v>
+      </c>
+      <c r="F29" s="6">
+        <f t="shared" si="0"/>
+        <v>6.0952380952380949</v>
+      </c>
+      <c r="G29" s="14">
+        <f>_xlfn.XLOOKUP(B29,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H29" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B29,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B30" s="34" t="s">
         <v>279</v>
       </c>
@@ -21148,8 +21603,24 @@
       <c r="D30" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E30" s="6">
+        <f>_xlfn.XLOOKUP(B30,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>180</v>
+      </c>
+      <c r="F30" s="6">
+        <f t="shared" si="0"/>
+        <v>2.2222222222222223</v>
+      </c>
+      <c r="G30" s="14">
+        <f>_xlfn.XLOOKUP(B30,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H30" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B30,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B31" s="34" t="s">
         <v>286</v>
       </c>
@@ -21159,8 +21630,24 @@
       <c r="D31" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E31" s="6">
+        <f>_xlfn.XLOOKUP(B31,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>200</v>
+      </c>
+      <c r="F31" s="6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G31" s="14">
+        <f>_xlfn.XLOOKUP(B31,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H31" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B31,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B32" s="34" t="s">
         <v>291</v>
       </c>
@@ -21170,8 +21657,24 @@
       <c r="D32" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E32" s="6">
+        <f>_xlfn.XLOOKUP(B32,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>240</v>
+      </c>
+      <c r="F32" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G32" s="14">
+        <f>_xlfn.XLOOKUP(B32,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H32" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B32,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B33" s="34" t="s">
         <v>297</v>
       </c>
@@ -21181,8 +21684,24 @@
       <c r="D33" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E33" s="6">
+        <f>_xlfn.XLOOKUP(B33,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>200</v>
+      </c>
+      <c r="F33" s="6">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G33" s="14">
+        <f>_xlfn.XLOOKUP(B33,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H33" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B33,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B34" s="34" t="s">
         <v>300</v>
       </c>
@@ -21192,8 +21711,24 @@
       <c r="D34" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E34" s="6">
+        <f>_xlfn.XLOOKUP(B34,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>200</v>
+      </c>
+      <c r="F34" s="6">
+        <f t="shared" si="0"/>
+        <v>2.4</v>
+      </c>
+      <c r="G34" s="14">
+        <f>_xlfn.XLOOKUP(B34,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H34" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B34,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B35" s="34" t="s">
         <v>308</v>
       </c>
@@ -21203,8 +21738,24 @@
       <c r="D35" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E35" s="6">
+        <f>_xlfn.XLOOKUP(B35,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>126</v>
+      </c>
+      <c r="F35" s="6">
+        <f t="shared" si="0"/>
+        <v>1.5238095238095237</v>
+      </c>
+      <c r="G35" s="14">
+        <f>_xlfn.XLOOKUP(B35,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H35" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B35,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B36" s="34" t="s">
         <v>310</v>
       </c>
@@ -21214,8 +21765,24 @@
       <c r="D36" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E36" s="6">
+        <f>_xlfn.XLOOKUP(B36,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>126</v>
+      </c>
+      <c r="F36" s="6">
+        <f t="shared" si="0"/>
+        <v>3.8095238095238093</v>
+      </c>
+      <c r="G36" s="14">
+        <f>_xlfn.XLOOKUP(B36,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H36" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B36,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B37" s="34" t="s">
         <v>513</v>
       </c>
@@ -21225,8 +21792,24 @@
       <c r="D37" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E37" s="6">
+        <f>_xlfn.XLOOKUP(B37,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>1000</v>
+      </c>
+      <c r="F37" s="6">
+        <f t="shared" si="0"/>
+        <v>6.1440000000000001</v>
+      </c>
+      <c r="G37" s="14">
+        <f>_xlfn.XLOOKUP(B37,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>24</v>
+      </c>
+      <c r="H37" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B37,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B38" s="34" t="s">
         <v>312</v>
       </c>
@@ -21236,8 +21819,24 @@
       <c r="D38" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E38" s="6">
+        <f>_xlfn.XLOOKUP(B38,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>1125</v>
+      </c>
+      <c r="F38" s="6">
+        <f t="shared" si="0"/>
+        <v>4.4373333333333331</v>
+      </c>
+      <c r="G38" s="14">
+        <f>_xlfn.XLOOKUP(B38,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>32</v>
+      </c>
+      <c r="H38" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B38,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B39" s="34" t="s">
         <v>327</v>
       </c>
@@ -21247,8 +21846,24 @@
       <c r="D39" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E39" s="6">
+        <f>_xlfn.XLOOKUP(B39,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>250</v>
+      </c>
+      <c r="F39" s="6">
+        <f t="shared" si="0"/>
+        <v>0.48</v>
+      </c>
+      <c r="G39" s="14">
+        <f>_xlfn.XLOOKUP(B39,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>1</v>
+      </c>
+      <c r="H39" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B39,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B40" s="34" t="s">
         <v>358</v>
       </c>
@@ -21258,8 +21873,24 @@
       <c r="D40" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E40" s="6">
+        <f>_xlfn.XLOOKUP(B40,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>220</v>
+      </c>
+      <c r="F40" s="6">
+        <f t="shared" si="0"/>
+        <v>3.9272727272727272</v>
+      </c>
+      <c r="G40" s="14">
+        <f>_xlfn.XLOOKUP(B40,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>3</v>
+      </c>
+      <c r="H40" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B40,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B41" s="34" t="s">
         <v>359</v>
       </c>
@@ -21269,8 +21900,24 @@
       <c r="D41" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E41" s="6">
+        <f>_xlfn.XLOOKUP(B41,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>220</v>
+      </c>
+      <c r="F41" s="6">
+        <f t="shared" si="0"/>
+        <v>1.9636363636363636</v>
+      </c>
+      <c r="G41" s="14">
+        <f>_xlfn.XLOOKUP(B41,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>3</v>
+      </c>
+      <c r="H41" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B41,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B42" s="34" t="s">
         <v>361</v>
       </c>
@@ -21280,8 +21927,24 @@
       <c r="D42" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E42" s="6">
+        <f>_xlfn.XLOOKUP(B42,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>220</v>
+      </c>
+      <c r="F42" s="6">
+        <f t="shared" si="0"/>
+        <v>1.9636363636363636</v>
+      </c>
+      <c r="G42" s="14">
+        <f>_xlfn.XLOOKUP(B42,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>3</v>
+      </c>
+      <c r="H42" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B42,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B43" s="34" t="s">
         <v>280</v>
       </c>
@@ -21291,8 +21954,24 @@
       <c r="D43" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E43" s="6">
+        <f>_xlfn.XLOOKUP(B43,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>180</v>
+      </c>
+      <c r="F43" s="6">
+        <f t="shared" si="0"/>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="G43" s="14">
+        <f>_xlfn.XLOOKUP(B43,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H43" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B43,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B44" s="34" t="s">
         <v>365</v>
       </c>
@@ -21302,8 +21981,24 @@
       <c r="D44" s="37">
         <v>46175</v>
       </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E44" s="6">
+        <f>_xlfn.XLOOKUP(B44,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>220</v>
+      </c>
+      <c r="F44" s="6">
+        <f t="shared" si="0"/>
+        <v>1.6</v>
+      </c>
+      <c r="G44" s="14">
+        <f>_xlfn.XLOOKUP(B44,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H44" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B44,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B45" s="34" t="s">
         <v>369</v>
       </c>
@@ -21313,8 +22008,24 @@
       <c r="D45" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E45" s="6">
+        <f>_xlfn.XLOOKUP(B45,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>220</v>
+      </c>
+      <c r="F45" s="6">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="G45" s="14">
+        <f>_xlfn.XLOOKUP(B45,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H45" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B45,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B46" s="34" t="s">
         <v>370</v>
       </c>
@@ -21324,8 +22035,24 @@
       <c r="D46" s="37">
         <v>46177</v>
       </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E46" s="6">
+        <f>_xlfn.XLOOKUP(B46,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>220</v>
+      </c>
+      <c r="F46" s="6">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="G46" s="14">
+        <f>_xlfn.XLOOKUP(B46,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H46" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B46,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B47" s="34" t="s">
         <v>371</v>
       </c>
@@ -21335,8 +22062,24 @@
       <c r="D47" s="37">
         <v>46177</v>
       </c>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E47" s="6">
+        <f>_xlfn.XLOOKUP(B47,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>300</v>
+      </c>
+      <c r="F47" s="6">
+        <f t="shared" si="0"/>
+        <v>2.3466666666666667</v>
+      </c>
+      <c r="G47" s="14">
+        <f>_xlfn.XLOOKUP(B47,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H47" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B47,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B48" s="34" t="s">
         <v>301</v>
       </c>
@@ -21346,8 +22089,24 @@
       <c r="D48" s="37">
         <v>46177</v>
       </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E48" s="6">
+        <f>_xlfn.XLOOKUP(B48,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>180</v>
+      </c>
+      <c r="F48" s="6">
+        <f t="shared" si="0"/>
+        <v>1.9555555555555555</v>
+      </c>
+      <c r="G48" s="14">
+        <f>_xlfn.XLOOKUP(B48,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H48" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B48,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B49" s="34" t="s">
         <v>313</v>
       </c>
@@ -21357,8 +22116,24 @@
       <c r="D49" s="37">
         <v>46177</v>
       </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E49" s="6">
+        <f>_xlfn.XLOOKUP(B49,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>3000</v>
+      </c>
+      <c r="F49" s="6">
+        <f t="shared" si="0"/>
+        <v>3.0720000000000001</v>
+      </c>
+      <c r="G49" s="14">
+        <f>_xlfn.XLOOKUP(B49,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>48</v>
+      </c>
+      <c r="H49" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B49,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B50" s="34" t="s">
         <v>253</v>
       </c>
@@ -21368,8 +22143,24 @@
       <c r="D50" s="37">
         <v>46177</v>
       </c>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E50" s="6">
+        <f>_xlfn.XLOOKUP(B50,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>300</v>
+      </c>
+      <c r="F50" s="6">
+        <f t="shared" si="0"/>
+        <v>0.84</v>
+      </c>
+      <c r="G50" s="14">
+        <f>_xlfn.XLOOKUP(B50,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H50" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B50,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B51" s="34" t="s">
         <v>377</v>
       </c>
@@ -21379,8 +22170,24 @@
       <c r="D51" s="37">
         <v>46177</v>
       </c>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E51" s="6">
+        <f>_xlfn.XLOOKUP(B51,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>152</v>
+      </c>
+      <c r="F51" s="6">
+        <f t="shared" si="0"/>
+        <v>2.3157894736842106</v>
+      </c>
+      <c r="G51" s="14">
+        <f>_xlfn.XLOOKUP(B51,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H51" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B51,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B52" s="34" t="s">
         <v>314</v>
       </c>
@@ -21390,8 +22197,24 @@
       <c r="D52" s="37">
         <v>46177</v>
       </c>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E52" s="6">
+        <f>_xlfn.XLOOKUP(B52,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>2304</v>
+      </c>
+      <c r="F52" s="6">
+        <f t="shared" si="0"/>
+        <v>3.71875</v>
+      </c>
+      <c r="G52" s="14">
+        <f>_xlfn.XLOOKUP(B52,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>34</v>
+      </c>
+      <c r="H52" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B52,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B53" s="34" t="s">
         <v>236</v>
       </c>
@@ -21401,8 +22224,24 @@
       <c r="D53" s="37">
         <v>46195</v>
       </c>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E53" s="6">
+        <f>_xlfn.XLOOKUP(B53,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>2304</v>
+      </c>
+      <c r="F53" s="6">
+        <f t="shared" si="0"/>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="G53" s="14">
+        <f>_xlfn.XLOOKUP(B53,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>32</v>
+      </c>
+      <c r="H53" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B53,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B54" s="37" t="s">
         <v>241</v>
       </c>
@@ -21412,8 +22251,24 @@
       <c r="D54" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E54" s="6">
+        <f>_xlfn.XLOOKUP(B54,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>2304</v>
+      </c>
+      <c r="F54" s="6">
+        <f t="shared" si="0"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="G54" s="14">
+        <f>_xlfn.XLOOKUP(B54,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>32</v>
+      </c>
+      <c r="H54" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B54,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B55" s="37" t="s">
         <v>254</v>
       </c>
@@ -21423,8 +22278,24 @@
       <c r="D55" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E55" s="6">
+        <f>_xlfn.XLOOKUP(B55,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>245</v>
+      </c>
+      <c r="F55" s="6">
+        <f t="shared" si="0"/>
+        <v>1.0285714285714285</v>
+      </c>
+      <c r="G55" s="14">
+        <f>_xlfn.XLOOKUP(B55,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H55" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B55,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B56" s="37" t="s">
         <v>255</v>
       </c>
@@ -21434,8 +22305,24 @@
       <c r="D56" s="37">
         <v>46202</v>
       </c>
-    </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E56" s="6">
+        <f>_xlfn.XLOOKUP(B56,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>300</v>
+      </c>
+      <c r="F56" s="6">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="G56" s="14">
+        <f>_xlfn.XLOOKUP(B56,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>30</v>
+      </c>
+      <c r="H56" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B56,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B57" s="37" t="s">
         <v>260</v>
       </c>
@@ -21445,8 +22332,24 @@
       <c r="D57" s="37">
         <v>46178</v>
       </c>
-    </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E57" s="6">
+        <f>_xlfn.XLOOKUP(B57,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>260</v>
+      </c>
+      <c r="F57" s="6">
+        <f t="shared" si="0"/>
+        <v>58.584615384615383</v>
+      </c>
+      <c r="G57" s="14">
+        <f>_xlfn.XLOOKUP(B57,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H57" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B57,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B58" s="37" t="s">
         <v>376</v>
       </c>
@@ -21456,8 +22359,24 @@
       <c r="D58" s="37">
         <v>46186</v>
       </c>
-    </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E58" s="6">
+        <f>_xlfn.XLOOKUP(B58,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>1824</v>
+      </c>
+      <c r="F58" s="6">
+        <f t="shared" si="0"/>
+        <v>40.263157894736842</v>
+      </c>
+      <c r="G58" s="14">
+        <f>_xlfn.XLOOKUP(B58,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>24</v>
+      </c>
+      <c r="H58" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B58,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B59" s="37" t="s">
         <v>287</v>
       </c>
@@ -21467,8 +22386,24 @@
       <c r="D59" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E59" s="6">
+        <f>_xlfn.XLOOKUP(B59,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>200</v>
+      </c>
+      <c r="F59" s="6">
+        <f t="shared" si="0"/>
+        <v>1.92</v>
+      </c>
+      <c r="G59" s="14">
+        <f>_xlfn.XLOOKUP(B59,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H59" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B59,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B60" s="37" t="s">
         <v>298</v>
       </c>
@@ -21478,8 +22413,24 @@
       <c r="D60" s="37">
         <v>46177</v>
       </c>
-    </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E60" s="6">
+        <f>_xlfn.XLOOKUP(B60,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>200</v>
+      </c>
+      <c r="F60" s="6">
+        <f t="shared" si="0"/>
+        <v>1.92</v>
+      </c>
+      <c r="G60" s="14">
+        <f>_xlfn.XLOOKUP(B60,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H60" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B60,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B61" s="37" t="s">
         <v>305</v>
       </c>
@@ -21489,8 +22440,24 @@
       <c r="D61" s="37">
         <v>46177</v>
       </c>
-    </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E61" s="6">
+        <f>_xlfn.XLOOKUP(B61,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>125</v>
+      </c>
+      <c r="F61" s="6">
+        <f t="shared" si="0"/>
+        <v>4.6079999999999997</v>
+      </c>
+      <c r="G61" s="14">
+        <f>_xlfn.XLOOKUP(B61,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>3</v>
+      </c>
+      <c r="H61" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B61,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B62" s="37" t="s">
         <v>261</v>
       </c>
@@ -21500,8 +22467,24 @@
       <c r="D62" s="37">
         <v>46177</v>
       </c>
-    </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E62" s="6">
+        <f>_xlfn.XLOOKUP(B62,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>240</v>
+      </c>
+      <c r="F62" s="6">
+        <f t="shared" si="0"/>
+        <v>1.0666666666666667</v>
+      </c>
+      <c r="G62" s="14">
+        <f>_xlfn.XLOOKUP(B62,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H62" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B62,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B63" s="37" t="s">
         <v>328</v>
       </c>
@@ -21511,8 +22494,24 @@
       <c r="D63" s="37">
         <v>46175</v>
       </c>
-    </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E63" s="6">
+        <f>_xlfn.XLOOKUP(B63,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>250</v>
+      </c>
+      <c r="F63" s="6">
+        <f t="shared" si="0"/>
+        <v>1.536</v>
+      </c>
+      <c r="G63" s="14">
+        <f>_xlfn.XLOOKUP(B63,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H63" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B63,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B64" s="37" t="s">
         <v>265</v>
       </c>
@@ -21522,8 +22521,24 @@
       <c r="D64" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E64" s="6">
+        <f>_xlfn.XLOOKUP(B64,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>60</v>
+      </c>
+      <c r="F64" s="6">
+        <f t="shared" si="0"/>
+        <v>4.2666666666666666</v>
+      </c>
+      <c r="G64" s="14">
+        <f>_xlfn.XLOOKUP(B64,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>1</v>
+      </c>
+      <c r="H64" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B64,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B65" s="37" t="s">
         <v>352</v>
       </c>
@@ -21533,8 +22548,24 @@
       <c r="D65" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E65" s="6">
+        <f>_xlfn.XLOOKUP(B65,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>100</v>
+      </c>
+      <c r="F65" s="6">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G65" s="14">
+        <f>_xlfn.XLOOKUP(B65,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>1</v>
+      </c>
+      <c r="H65" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B65,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="37" t="s">
         <v>341</v>
       </c>
@@ -21544,8 +22575,24 @@
       <c r="D66" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E66" s="6">
+        <f>_xlfn.XLOOKUP(B66,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>2268</v>
+      </c>
+      <c r="F66" s="6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G66" s="14">
+        <f>_xlfn.XLOOKUP(B66,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>21</v>
+      </c>
+      <c r="H66" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B66,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B67" s="37" t="s">
         <v>348</v>
       </c>
@@ -21555,8 +22602,24 @@
       <c r="D67" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E67" s="6">
+        <f>_xlfn.XLOOKUP(B67,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>2268</v>
+      </c>
+      <c r="F67" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G67" s="14">
+        <f>_xlfn.XLOOKUP(B67,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>21</v>
+      </c>
+      <c r="H67" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B67,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B68" s="37" t="s">
         <v>362</v>
       </c>
@@ -21566,8 +22629,24 @@
       <c r="D68" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E68" s="6">
+        <f>_xlfn.XLOOKUP(B68,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>220</v>
+      </c>
+      <c r="F68" s="6">
+        <f t="shared" si="0"/>
+        <v>0.98181818181818181</v>
+      </c>
+      <c r="G68" s="14">
+        <f>_xlfn.XLOOKUP(B68,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>3</v>
+      </c>
+      <c r="H68" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B68,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B69" s="37" t="s">
         <v>364</v>
       </c>
@@ -21577,8 +22656,24 @@
       <c r="D69" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E69" s="6">
+        <f>_xlfn.XLOOKUP(B69,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>220</v>
+      </c>
+      <c r="F69" s="6">
+        <f t="shared" si="0"/>
+        <v>0.98181818181818181</v>
+      </c>
+      <c r="G69" s="14">
+        <f>_xlfn.XLOOKUP(B69,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>3</v>
+      </c>
+      <c r="H69" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B69,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B70" s="37" t="s">
         <v>321</v>
       </c>
@@ -21588,8 +22683,24 @@
       <c r="D70" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E70" s="6">
+        <f>_xlfn.XLOOKUP(B70,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>220</v>
+      </c>
+      <c r="F70" s="6">
+        <f t="shared" ref="F70:F85" si="1">(G70*C70)/E70</f>
+        <v>4.9090909090909092</v>
+      </c>
+      <c r="G70" s="14">
+        <f>_xlfn.XLOOKUP(B70,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>3</v>
+      </c>
+      <c r="H70" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B70,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B71" s="37" t="s">
         <v>375</v>
       </c>
@@ -21599,8 +22710,24 @@
       <c r="D71" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E71" s="6">
+        <f>_xlfn.XLOOKUP(B71,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>960</v>
+      </c>
+      <c r="F71" s="6">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="G71" s="14">
+        <f>_xlfn.XLOOKUP(B71,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>30</v>
+      </c>
+      <c r="H71" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B71,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B72" s="37" t="s">
         <v>307</v>
       </c>
@@ -21610,8 +22737,24 @@
       <c r="D72" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E72" s="6">
+        <f>_xlfn.XLOOKUP(B72,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>125</v>
+      </c>
+      <c r="F72" s="6">
+        <f t="shared" si="1"/>
+        <v>4.6079999999999997</v>
+      </c>
+      <c r="G72" s="14">
+        <f>_xlfn.XLOOKUP(B72,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>3</v>
+      </c>
+      <c r="H72" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B72,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B73" s="37" t="s">
         <v>293</v>
       </c>
@@ -21621,8 +22764,24 @@
       <c r="D73" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E73" s="6">
+        <f>_xlfn.XLOOKUP(B73,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>300</v>
+      </c>
+      <c r="F73" s="6">
+        <f t="shared" si="1"/>
+        <v>0.84</v>
+      </c>
+      <c r="G73" s="14">
+        <f>_xlfn.XLOOKUP(B73,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H73" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B73,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B74" s="37" t="s">
         <v>282</v>
       </c>
@@ -21632,8 +22791,24 @@
       <c r="D74" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E74" s="6">
+        <f>_xlfn.XLOOKUP(B74,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>300</v>
+      </c>
+      <c r="F74" s="6">
+        <f t="shared" si="1"/>
+        <v>0.84</v>
+      </c>
+      <c r="G74" s="14">
+        <f>_xlfn.XLOOKUP(B74,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H74" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B74,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B75" s="37" t="s">
         <v>333</v>
       </c>
@@ -21643,8 +22818,24 @@
       <c r="D75" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E75" s="6">
+        <f>_xlfn.XLOOKUP(B75,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>300</v>
+      </c>
+      <c r="F75" s="6">
+        <f t="shared" si="1"/>
+        <v>0.84</v>
+      </c>
+      <c r="G75" s="14">
+        <f>_xlfn.XLOOKUP(B75,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H75" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B75,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B76" s="37" t="s">
         <v>325</v>
       </c>
@@ -21654,8 +22845,24 @@
       <c r="D76" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E76" s="6">
+        <f>_xlfn.XLOOKUP(B76,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>250</v>
+      </c>
+      <c r="F76" s="6">
+        <f t="shared" si="1"/>
+        <v>5.1040000000000001</v>
+      </c>
+      <c r="G76" s="14">
+        <f>_xlfn.XLOOKUP(B76,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>1</v>
+      </c>
+      <c r="H76" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B76,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="37" t="s">
         <v>326</v>
       </c>
@@ -21665,8 +22872,24 @@
       <c r="D77" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E77" s="6">
+        <f>_xlfn.XLOOKUP(B77,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>180</v>
+      </c>
+      <c r="F77" s="6">
+        <f t="shared" si="1"/>
+        <v>4.2666666666666666</v>
+      </c>
+      <c r="G77" s="14">
+        <f>_xlfn.XLOOKUP(B77,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>1</v>
+      </c>
+      <c r="H77" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B77,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="78" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B78" s="37" t="s">
         <v>296</v>
       </c>
@@ -21676,8 +22899,24 @@
       <c r="D78" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E78" s="6">
+        <f>_xlfn.XLOOKUP(B78,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>220</v>
+      </c>
+      <c r="F78" s="6">
+        <f t="shared" si="1"/>
+        <v>4.0727272727272723</v>
+      </c>
+      <c r="G78" s="14">
+        <f>_xlfn.XLOOKUP(B78,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>1</v>
+      </c>
+      <c r="H78" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B78,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="37" t="s">
         <v>329</v>
       </c>
@@ -21687,8 +22926,24 @@
       <c r="D79" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E79" s="6">
+        <f>_xlfn.XLOOKUP(B79,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>250</v>
+      </c>
+      <c r="F79" s="6">
+        <f t="shared" si="1"/>
+        <v>1.024</v>
+      </c>
+      <c r="G79" s="14">
+        <f>_xlfn.XLOOKUP(B79,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>1</v>
+      </c>
+      <c r="H79" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B79,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B80" s="37" t="s">
         <v>223</v>
       </c>
@@ -21698,8 +22953,24 @@
       <c r="D80" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="81" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E80" s="6">
+        <f>_xlfn.XLOOKUP(B80,Table4[ref_id],Table4[tempo_L2_prod_min (cadência de L2)])</f>
+        <v>250</v>
+      </c>
+      <c r="F80" s="6">
+        <f t="shared" si="1"/>
+        <v>0.70399999999999996</v>
+      </c>
+      <c r="G80" s="14">
+        <f>_xlfn.XLOOKUP(B80,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H80" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B80,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B81" s="37" t="s">
         <v>330</v>
       </c>
@@ -21709,8 +22980,24 @@
       <c r="D81" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="82" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E81" s="6">
+        <f>_xlfn.XLOOKUP(B81,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>180</v>
+      </c>
+      <c r="F81" s="6">
+        <f t="shared" si="1"/>
+        <v>0.62222222222222223</v>
+      </c>
+      <c r="G81" s="14">
+        <f>_xlfn.XLOOKUP(B81,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>1</v>
+      </c>
+      <c r="H81" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B81,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B82" s="37" t="s">
         <v>226</v>
       </c>
@@ -21720,8 +23007,24 @@
       <c r="D82" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="83" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E82" s="6">
+        <f>_xlfn.XLOOKUP(B82,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>180</v>
+      </c>
+      <c r="F82" s="6">
+        <f t="shared" si="1"/>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="G82" s="14">
+        <f>_xlfn.XLOOKUP(B82,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H82" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B82,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B83" s="37" t="s">
         <v>270</v>
       </c>
@@ -21731,8 +23034,24 @@
       <c r="D83" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="84" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E83" s="6">
+        <f>_xlfn.XLOOKUP(B83,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>240</v>
+      </c>
+      <c r="F83" s="6">
+        <f t="shared" si="1"/>
+        <v>0.9</v>
+      </c>
+      <c r="G83" s="14">
+        <f>_xlfn.XLOOKUP(B83,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>3</v>
+      </c>
+      <c r="H83" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B83,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B84" s="37" t="s">
         <v>288</v>
       </c>
@@ -21742,8 +23061,24 @@
       <c r="D84" s="37">
         <v>46203</v>
       </c>
-    </row>
-    <row r="85" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E84" s="6">
+        <f>_xlfn.XLOOKUP(B84,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>200</v>
+      </c>
+      <c r="F84" s="6">
+        <f t="shared" si="1"/>
+        <v>0.96</v>
+      </c>
+      <c r="G84" s="14">
+        <f>_xlfn.XLOOKUP(B84,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H84" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B84,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B85" s="37" t="s">
         <v>225</v>
       </c>
@@ -21752,6 +23087,319 @@
       </c>
       <c r="D85" s="37">
         <v>46203</v>
+      </c>
+      <c r="E85" s="6">
+        <f>_xlfn.XLOOKUP(B85,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>180</v>
+      </c>
+      <c r="F85" s="6">
+        <f t="shared" si="1"/>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="G85" s="14">
+        <f>_xlfn.XLOOKUP(B85,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H85" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B85,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B86" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="C86" s="14">
+        <v>256</v>
+      </c>
+      <c r="D86" s="38">
+        <v>46203</v>
+      </c>
+      <c r="E86" s="6">
+        <f>_xlfn.XLOOKUP(B86,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>250</v>
+      </c>
+      <c r="F86" s="6">
+        <f t="shared" ref="F86:F96" si="2">(G86*C86)/E86</f>
+        <v>1.024</v>
+      </c>
+      <c r="G86" s="14">
+        <f>_xlfn.XLOOKUP(B86,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>1</v>
+      </c>
+      <c r="H86" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B86,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B87" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C87" s="14">
+        <v>512</v>
+      </c>
+      <c r="D87" s="38">
+        <v>46203</v>
+      </c>
+      <c r="E87" s="6">
+        <f>_xlfn.XLOOKUP(B87,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>180</v>
+      </c>
+      <c r="F87" s="6">
+        <f t="shared" si="2"/>
+        <v>2.8444444444444446</v>
+      </c>
+      <c r="G87" s="14">
+        <f>_xlfn.XLOOKUP(B87,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>1</v>
+      </c>
+      <c r="H87" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B87,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B88" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="C88" s="14">
+        <v>108</v>
+      </c>
+      <c r="D88" s="38">
+        <v>46203</v>
+      </c>
+      <c r="E88" s="6">
+        <f>_xlfn.XLOOKUP(B88,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>2268</v>
+      </c>
+      <c r="F88" s="6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G88" s="14">
+        <f>_xlfn.XLOOKUP(B88,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>21</v>
+      </c>
+      <c r="H88" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B88,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B89" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C89" s="14">
+        <v>156</v>
+      </c>
+      <c r="D89" s="38">
+        <v>46203</v>
+      </c>
+      <c r="E89" s="6">
+        <f>_xlfn.XLOOKUP(B89,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>134</v>
+      </c>
+      <c r="F89" s="6">
+        <f t="shared" si="2"/>
+        <v>2.3283582089552239</v>
+      </c>
+      <c r="G89" s="14">
+        <f>_xlfn.XLOOKUP(B89,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H89" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B89,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B90" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C90" s="14">
+        <v>108</v>
+      </c>
+      <c r="D90" s="38">
+        <v>46203</v>
+      </c>
+      <c r="E90" s="6">
+        <f>_xlfn.XLOOKUP(B90,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>2268</v>
+      </c>
+      <c r="F90" s="6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G90" s="14">
+        <f>_xlfn.XLOOKUP(B90,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>21</v>
+      </c>
+      <c r="H90" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B90,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B91" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C91" s="14">
+        <v>140</v>
+      </c>
+      <c r="D91" s="38">
+        <v>46203</v>
+      </c>
+      <c r="E91" s="6" cm="1">
+        <f t="array" ref="E91">_xlfn.XLOOKUP(B91,Table4[ref_id],'2_REFERENCIAS'!$L$5:$L$192)</f>
+        <v>800</v>
+      </c>
+      <c r="F91" s="6">
+        <f t="shared" si="2"/>
+        <v>7.875</v>
+      </c>
+      <c r="G91" s="14">
+        <f>_xlfn.XLOOKUP(B91,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>45</v>
+      </c>
+      <c r="H91" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B91,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B92" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="C92" s="14">
+        <v>108</v>
+      </c>
+      <c r="D92" s="38">
+        <v>46203</v>
+      </c>
+      <c r="E92" s="6">
+        <f>_xlfn.XLOOKUP(B92,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>2268</v>
+      </c>
+      <c r="F92" s="6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G92" s="14">
+        <f>_xlfn.XLOOKUP(B92,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>21</v>
+      </c>
+      <c r="H92" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B92,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B93" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="C93" s="14">
+        <v>378</v>
+      </c>
+      <c r="D93" s="38">
+        <v>46203</v>
+      </c>
+      <c r="E93" s="6">
+        <f>_xlfn.XLOOKUP(B93,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>350</v>
+      </c>
+      <c r="F93" s="6">
+        <f t="shared" si="2"/>
+        <v>4.32</v>
+      </c>
+      <c r="G93" s="14">
+        <f>_xlfn.XLOOKUP(B93,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H93" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B93,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B94" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="C94" s="14">
+        <v>315</v>
+      </c>
+      <c r="D94" s="38">
+        <v>46203</v>
+      </c>
+      <c r="E94" s="6">
+        <f>_xlfn.XLOOKUP(B94,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>350</v>
+      </c>
+      <c r="F94" s="6">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="G94" s="14">
+        <f>_xlfn.XLOOKUP(B94,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
+      </c>
+      <c r="H94" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B94,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B95" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C95" s="14">
+        <v>140</v>
+      </c>
+      <c r="D95" s="38">
+        <v>46203</v>
+      </c>
+      <c r="E95" s="6" cm="1">
+        <f t="array" ref="E95">_xlfn.XLOOKUP(B95,Table4[ref_id],'2_REFERENCIAS'!$L$5:$L$192)</f>
+        <v>672</v>
+      </c>
+      <c r="F95" s="6">
+        <f t="shared" si="2"/>
+        <v>7.5</v>
+      </c>
+      <c r="G95" s="14">
+        <f>_xlfn.XLOOKUP(B95,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>36</v>
+      </c>
+      <c r="H95" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B95,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B96" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="C96" s="14">
+        <v>96</v>
+      </c>
+      <c r="D96" s="38">
+        <v>46203</v>
+      </c>
+      <c r="E96" s="6">
+        <f>_xlfn.XLOOKUP(B96,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)])</f>
+        <v>126</v>
+      </c>
+      <c r="F96" s="6">
+        <f t="shared" si="2"/>
+        <v>1.5238095238095237</v>
+      </c>
+      <c r="G96" s="14">
+        <f>_xlfn.XLOOKUP(B96,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
+      </c>
+      <c r="H96" s="14" t="str">
+        <f>_xlfn.XLOOKUP(B96,Table4[ref_id],Table4[pode_L1])</f>
+        <v>Sim</v>
       </c>
     </row>
   </sheetData>
